--- a/research/traditional_assets/database/data/qatar/qatar_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_oil_gas_distribution.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0740439446345495</v>
+        <v>0.07401040068991493</v>
       </c>
       <c r="C2">
-        <v>12351.77100013611</v>
+        <v>12247.10927377859</v>
       </c>
       <c r="D2">
-        <v>11997.07100013611</v>
+        <v>12011.33627377859</v>
       </c>
       <c r="E2">
-        <v>-5578.6</v>
+        <v>-5459.673000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>118.927</v>
       </c>
       <c r="G2">
         <v>354.7</v>
@@ -1457,28 +1457,28 @@
         <v>706.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.9820281</v>
       </c>
       <c r="N2">
-        <v>706.7</v>
+        <v>700.7179719000001</v>
       </c>
       <c r="O2">
-        <v>70.67</v>
+        <v>70.07179719000001</v>
       </c>
       <c r="P2">
-        <v>636.0300000000001</v>
+        <v>630.6461747100001</v>
       </c>
       <c r="Q2">
-        <v>876.8300000000002</v>
+        <v>871.4461747100002</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0740439446345495</v>
+        <v>0.07430070776759085</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5712584956040617</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>118.137191632383</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07401040068991493</v>
+        <v>0.07397685674528039</v>
       </c>
       <c r="C3">
-        <v>12247.10927377859</v>
+        <v>12142.4815124267</v>
       </c>
       <c r="D3">
-        <v>12011.33627377859</v>
+        <v>12025.6355124267</v>
       </c>
       <c r="E3">
-        <v>-5459.673000000001</v>
+        <v>-5340.746</v>
       </c>
       <c r="F3">
-        <v>118.927</v>
+        <v>237.854</v>
       </c>
       <c r="G3">
         <v>354.7</v>
@@ -1539,28 +1539,28 @@
         <v>706.7</v>
       </c>
       <c r="M3">
-        <v>5.9820281</v>
+        <v>11.9640562</v>
       </c>
       <c r="N3">
-        <v>700.7179719000001</v>
+        <v>694.7359438000001</v>
       </c>
       <c r="O3">
-        <v>70.07179719000001</v>
+        <v>69.47359438000001</v>
       </c>
       <c r="P3">
-        <v>630.6461747100001</v>
+        <v>625.2623494200001</v>
       </c>
       <c r="Q3">
-        <v>871.4461747100002</v>
+        <v>866.0623494200001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07430070776759085</v>
+        <v>0.07456271096457183</v>
       </c>
       <c r="T3">
-        <v>0.5712584956040617</v>
+        <v>0.5765099985972963</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>118.137191632383</v>
+        <v>59.06859581619151</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07397685674528039</v>
+        <v>0.07394331280064584</v>
       </c>
       <c r="C4">
-        <v>12142.4815124267</v>
+        <v>12037.88783752889</v>
       </c>
       <c r="D4">
-        <v>12025.6355124267</v>
+        <v>12039.96883752889</v>
       </c>
       <c r="E4">
-        <v>-5340.746</v>
+        <v>-5221.819</v>
       </c>
       <c r="F4">
-        <v>237.854</v>
+        <v>356.781</v>
       </c>
       <c r="G4">
         <v>354.7</v>
@@ -1621,28 +1621,28 @@
         <v>706.7</v>
       </c>
       <c r="M4">
-        <v>11.9640562</v>
+        <v>17.9460843</v>
       </c>
       <c r="N4">
-        <v>694.7359438000001</v>
+        <v>688.7539157</v>
       </c>
       <c r="O4">
-        <v>69.47359438000001</v>
+        <v>68.87539157000001</v>
       </c>
       <c r="P4">
-        <v>625.2623494200001</v>
+        <v>619.87852413</v>
       </c>
       <c r="Q4">
-        <v>866.0623494200001</v>
+        <v>860.6785241299999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07456271096457183</v>
+        <v>0.07483011628932561</v>
       </c>
       <c r="T4">
-        <v>0.5765099985972963</v>
+        <v>0.5818697800027626</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.06859581619151</v>
+        <v>39.379063877461</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07394331280064584</v>
+        <v>0.07390976885601129</v>
       </c>
       <c r="C5">
-        <v>12037.88783752889</v>
+        <v>11933.32837111326</v>
       </c>
       <c r="D5">
-        <v>12039.96883752889</v>
+        <v>12054.33637111326</v>
       </c>
       <c r="E5">
-        <v>-5221.819</v>
+        <v>-5102.892000000001</v>
       </c>
       <c r="F5">
-        <v>356.781</v>
+        <v>475.708</v>
       </c>
       <c r="G5">
         <v>354.7</v>
@@ -1703,28 +1703,28 @@
         <v>706.7</v>
       </c>
       <c r="M5">
-        <v>17.9460843</v>
+        <v>23.9281124</v>
       </c>
       <c r="N5">
-        <v>688.7539157</v>
+        <v>682.7718876</v>
       </c>
       <c r="O5">
-        <v>68.87539157000001</v>
+        <v>68.27718876</v>
       </c>
       <c r="P5">
-        <v>619.87852413</v>
+        <v>614.49469884</v>
       </c>
       <c r="Q5">
-        <v>860.6785241299999</v>
+        <v>855.2946988399999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07483011628932561</v>
+        <v>0.0751030925583451</v>
       </c>
       <c r="T5">
-        <v>0.5818697800027626</v>
+        <v>0.5873412235208428</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.379063877461</v>
+        <v>29.53429790809575</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07390976885601129</v>
+        <v>0.07387622491137674</v>
       </c>
       <c r="C6">
-        <v>11933.32837111326</v>
+        <v>11828.80323579113</v>
       </c>
       <c r="D6">
-        <v>12054.33637111326</v>
+        <v>12068.73823579112</v>
       </c>
       <c r="E6">
-        <v>-5102.892000000001</v>
+        <v>-4983.965</v>
       </c>
       <c r="F6">
-        <v>475.708</v>
+        <v>594.6350000000001</v>
       </c>
       <c r="G6">
         <v>354.7</v>
@@ -1785,28 +1785,28 @@
         <v>706.7</v>
       </c>
       <c r="M6">
-        <v>23.9281124</v>
+        <v>29.9101405</v>
       </c>
       <c r="N6">
-        <v>682.7718876</v>
+        <v>676.7898595</v>
       </c>
       <c r="O6">
-        <v>68.27718876</v>
+        <v>67.67898595000001</v>
       </c>
       <c r="P6">
-        <v>614.49469884</v>
+        <v>609.1108735500001</v>
       </c>
       <c r="Q6">
-        <v>855.2946988399999</v>
+        <v>849.9108735500001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0751030925583451</v>
+        <v>0.07538181569618604</v>
       </c>
       <c r="T6">
-        <v>0.5873412235208428</v>
+        <v>0.592927855323514</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.53429790809575</v>
+        <v>23.6274383264766</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07387622491137674</v>
+        <v>0.07384268096674219</v>
       </c>
       <c r="C7">
-        <v>11828.80323579113</v>
+        <v>11724.31255476042</v>
       </c>
       <c r="D7">
-        <v>12068.73823579112</v>
+        <v>12083.17455476042</v>
       </c>
       <c r="E7">
-        <v>-4983.965</v>
+        <v>-4865.038</v>
       </c>
       <c r="F7">
-        <v>594.6350000000001</v>
+        <v>713.5620000000001</v>
       </c>
       <c r="G7">
         <v>354.7</v>
@@ -1867,28 +1867,28 @@
         <v>706.7</v>
       </c>
       <c r="M7">
-        <v>29.9101405</v>
+        <v>35.89216860000001</v>
       </c>
       <c r="N7">
-        <v>676.7898595</v>
+        <v>670.8078314000001</v>
       </c>
       <c r="O7">
-        <v>67.67898595000001</v>
+        <v>67.08078314000001</v>
       </c>
       <c r="P7">
-        <v>609.1108735500001</v>
+        <v>603.7270482600001</v>
       </c>
       <c r="Q7">
-        <v>849.9108735500001</v>
+        <v>844.5270482600001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07538181569618604</v>
+        <v>0.07566646911355553</v>
       </c>
       <c r="T7">
-        <v>0.592927855323514</v>
+        <v>0.5986333516326252</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.6274383264766</v>
+        <v>19.6895319387305</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07384268096674219</v>
+        <v>0.07380913702210765</v>
       </c>
       <c r="C8">
-        <v>11724.31255476042</v>
+        <v>11619.85645180929</v>
       </c>
       <c r="D8">
-        <v>12083.17455476042</v>
+        <v>12097.64545180929</v>
       </c>
       <c r="E8">
-        <v>-4865.038</v>
+        <v>-4746.111000000001</v>
       </c>
       <c r="F8">
-        <v>713.562</v>
+        <v>832.4889999999999</v>
       </c>
       <c r="G8">
         <v>354.7</v>
@@ -1949,28 +1949,28 @@
         <v>706.7</v>
       </c>
       <c r="M8">
-        <v>35.8921686</v>
+        <v>41.87419669999999</v>
       </c>
       <c r="N8">
-        <v>670.8078314000001</v>
+        <v>664.8258033000001</v>
       </c>
       <c r="O8">
-        <v>67.08078314000001</v>
+        <v>66.48258033</v>
       </c>
       <c r="P8">
-        <v>603.7270482600001</v>
+        <v>598.3432229700001</v>
       </c>
       <c r="Q8">
-        <v>844.5270482600001</v>
+        <v>839.1432229700001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07566646911355553</v>
+        <v>0.07595724410979317</v>
       </c>
       <c r="T8">
-        <v>0.5986333516326252</v>
+        <v>0.6044615467870935</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.6895319387305</v>
+        <v>16.876741661769</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07380913702210766</v>
+        <v>0.0737755930774731</v>
       </c>
       <c r="C9">
-        <v>11619.85645180929</v>
+        <v>11515.43505131955</v>
       </c>
       <c r="D9">
-        <v>12097.64545180929</v>
+        <v>12112.15105131955</v>
       </c>
       <c r="E9">
-        <v>-4746.111</v>
+        <v>-4627.184</v>
       </c>
       <c r="F9">
-        <v>832.4890000000001</v>
+        <v>951.4160000000001</v>
       </c>
       <c r="G9">
         <v>354.7</v>
@@ -2031,28 +2031,28 @@
         <v>706.7</v>
       </c>
       <c r="M9">
-        <v>41.87419670000001</v>
+        <v>47.8562248</v>
       </c>
       <c r="N9">
-        <v>664.8258033000001</v>
+        <v>658.8437752000001</v>
       </c>
       <c r="O9">
-        <v>66.48258033</v>
+        <v>65.88437752000002</v>
       </c>
       <c r="P9">
-        <v>598.3432229700001</v>
+        <v>592.9593976800001</v>
       </c>
       <c r="Q9">
-        <v>839.1432229700001</v>
+        <v>833.7593976800001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07595724410979318</v>
+        <v>0.07625434030160119</v>
       </c>
       <c r="T9">
-        <v>0.6044615467870936</v>
+        <v>0.6104164418362242</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.876741661769</v>
+        <v>14.76714895404788</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0737755930774731</v>
+        <v>0.07374204913283855</v>
       </c>
       <c r="C10">
-        <v>11515.43505131955</v>
+        <v>11411.04847827032</v>
       </c>
       <c r="D10">
-        <v>12112.15105131955</v>
+        <v>12126.69147827032</v>
       </c>
       <c r="E10">
-        <v>-4627.184</v>
+        <v>-4508.257000000001</v>
       </c>
       <c r="F10">
-        <v>951.4160000000001</v>
+        <v>1070.343</v>
       </c>
       <c r="G10">
         <v>354.7</v>
@@ -2113,28 +2113,28 @@
         <v>706.7</v>
       </c>
       <c r="M10">
-        <v>47.8562248</v>
+        <v>53.8382529</v>
       </c>
       <c r="N10">
-        <v>658.8437752000001</v>
+        <v>652.8617471</v>
       </c>
       <c r="O10">
-        <v>65.88437752000002</v>
+        <v>65.28617471</v>
       </c>
       <c r="P10">
-        <v>592.9593976800001</v>
+        <v>587.57557239</v>
       </c>
       <c r="Q10">
-        <v>833.7593976800001</v>
+        <v>828.3755723900001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07625434030160119</v>
+        <v>0.07655796608004235</v>
       </c>
       <c r="T10">
-        <v>0.6104164418362242</v>
+        <v>0.6165022136996214</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.76714895404788</v>
+        <v>13.12635462582033</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07374204913283855</v>
+        <v>0.073708505188204</v>
       </c>
       <c r="C11">
-        <v>11411.04847827032</v>
+        <v>11306.69685824155</v>
       </c>
       <c r="D11">
-        <v>12126.69147827032</v>
+        <v>12141.26685824155</v>
       </c>
       <c r="E11">
-        <v>-4508.257000000001</v>
+        <v>-4389.33</v>
       </c>
       <c r="F11">
-        <v>1070.343</v>
+        <v>1189.27</v>
       </c>
       <c r="G11">
         <v>354.7</v>
@@ -2195,28 +2195,28 @@
         <v>706.7</v>
       </c>
       <c r="M11">
-        <v>53.8382529</v>
+        <v>59.82028099999999</v>
       </c>
       <c r="N11">
-        <v>652.8617471</v>
+        <v>646.879719</v>
       </c>
       <c r="O11">
-        <v>65.28617471</v>
+        <v>64.68797190000001</v>
       </c>
       <c r="P11">
-        <v>587.57557239</v>
+        <v>582.1917471</v>
       </c>
       <c r="Q11">
-        <v>828.3755723900001</v>
+        <v>822.9917471000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07655796608004235</v>
+        <v>0.07686833909800445</v>
       </c>
       <c r="T11">
-        <v>0.6165022136996214</v>
+        <v>0.6227232249377611</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.12635462582033</v>
+        <v>11.8137191632383</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.073708505188204</v>
+        <v>0.07367496124356947</v>
       </c>
       <c r="C12">
-        <v>11306.69685824155</v>
+        <v>11202.38031741771</v>
       </c>
       <c r="D12">
-        <v>12141.26685824155</v>
+        <v>12155.87731741771</v>
       </c>
       <c r="E12">
-        <v>-4389.33</v>
+        <v>-4270.403</v>
       </c>
       <c r="F12">
-        <v>1189.27</v>
+        <v>1308.197</v>
       </c>
       <c r="G12">
         <v>354.7</v>
@@ -2277,28 +2277,28 @@
         <v>706.7</v>
       </c>
       <c r="M12">
-        <v>59.82028100000001</v>
+        <v>65.8023091</v>
       </c>
       <c r="N12">
-        <v>646.879719</v>
+        <v>640.8976909</v>
       </c>
       <c r="O12">
-        <v>64.68797190000001</v>
+        <v>64.08976909</v>
       </c>
       <c r="P12">
-        <v>582.1917471</v>
+        <v>576.80792181</v>
       </c>
       <c r="Q12">
-        <v>822.9917471000001</v>
+        <v>817.6079218100001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07686833909800445</v>
+        <v>0.07718568679052748</v>
       </c>
       <c r="T12">
-        <v>0.6227232249377611</v>
+        <v>0.6290840341812519</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.8137191632383</v>
+        <v>10.739744693853</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07367496124356947</v>
+        <v>0.07364141729893491</v>
       </c>
       <c r="C13">
-        <v>11202.38031741771</v>
+        <v>11098.09898259135</v>
       </c>
       <c r="D13">
-        <v>12155.87731741771</v>
+        <v>12170.52298259135</v>
       </c>
       <c r="E13">
-        <v>-4270.403</v>
+        <v>-4151.476000000001</v>
       </c>
       <c r="F13">
-        <v>1308.197</v>
+        <v>1427.124</v>
       </c>
       <c r="G13">
         <v>354.7</v>
@@ -2359,28 +2359,28 @@
         <v>706.7</v>
       </c>
       <c r="M13">
-        <v>65.8023091</v>
+        <v>71.7843372</v>
       </c>
       <c r="N13">
-        <v>640.8976909</v>
+        <v>634.9156628000001</v>
       </c>
       <c r="O13">
-        <v>64.08976909</v>
+        <v>63.49156628000001</v>
       </c>
       <c r="P13">
-        <v>576.80792181</v>
+        <v>571.42409652</v>
       </c>
       <c r="Q13">
-        <v>817.6079218100001</v>
+        <v>812.2240965200001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07718568679052748</v>
+        <v>0.07751024693060785</v>
       </c>
       <c r="T13">
-        <v>0.6290840341812519</v>
+        <v>0.6355894072711858</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.739744693853</v>
+        <v>9.844765969365252</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07364141729893491</v>
+        <v>0.07360787335430036</v>
       </c>
       <c r="C14">
-        <v>11098.09898259135</v>
+        <v>10993.85298116683</v>
       </c>
       <c r="D14">
-        <v>12170.52298259135</v>
+        <v>12185.20398116683</v>
       </c>
       <c r="E14">
-        <v>-4151.476000000001</v>
+        <v>-4032.549</v>
       </c>
       <c r="F14">
-        <v>1427.124</v>
+        <v>1546.051</v>
       </c>
       <c r="G14">
         <v>354.7</v>
@@ -2441,28 +2441,28 @@
         <v>706.7</v>
       </c>
       <c r="M14">
-        <v>71.7843372</v>
+        <v>77.7663653</v>
       </c>
       <c r="N14">
-        <v>634.9156628000001</v>
+        <v>628.9336347000001</v>
       </c>
       <c r="O14">
-        <v>63.49156628000001</v>
+        <v>62.89336347000001</v>
       </c>
       <c r="P14">
-        <v>571.42409652</v>
+        <v>566.04027123</v>
       </c>
       <c r="Q14">
-        <v>812.2240965200001</v>
+        <v>806.8402712300001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07751024693060785</v>
+        <v>0.07784226822333373</v>
       </c>
       <c r="T14">
-        <v>0.6355894072711858</v>
+        <v>0.6422443291677848</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.844765969365252</v>
+        <v>9.087476279414078</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07360787335430036</v>
+        <v>0.0737633294096658</v>
       </c>
       <c r="C15">
-        <v>10993.85298116683</v>
+        <v>10807.1849866313</v>
       </c>
       <c r="D15">
-        <v>12185.20398116683</v>
+        <v>12117.4629866313</v>
       </c>
       <c r="E15">
-        <v>-4032.549</v>
+        <v>-3913.622</v>
       </c>
       <c r="F15">
-        <v>1546.051</v>
+        <v>1664.978</v>
       </c>
       <c r="G15">
         <v>354.7</v>
@@ -2523,45 +2523,45 @@
         <v>706.7</v>
       </c>
       <c r="M15">
-        <v>77.7663653</v>
+        <v>86.24586040000001</v>
       </c>
       <c r="N15">
-        <v>628.9336347000001</v>
+        <v>620.4541396000001</v>
       </c>
       <c r="O15">
-        <v>62.89336347000001</v>
+        <v>62.04541396000001</v>
       </c>
       <c r="P15">
-        <v>566.04027123</v>
+        <v>558.4087256400001</v>
       </c>
       <c r="Q15">
-        <v>806.8402712300001</v>
+        <v>799.20872564</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07784226822333373</v>
+        <v>0.07818201094147187</v>
       </c>
       <c r="T15">
-        <v>0.6422443291677848</v>
+        <v>0.6490540166898862</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.087476279414078</v>
+        <v>8.194016463194796</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0737633294096658</v>
+        <v>0.07374328546503126</v>
       </c>
       <c r="C16">
-        <v>10807.1849866313</v>
+        <v>10696.94994082255</v>
       </c>
       <c r="D16">
-        <v>12117.4629866313</v>
+        <v>12126.15494082255</v>
       </c>
       <c r="E16">
-        <v>-3913.622</v>
+        <v>-3794.695</v>
       </c>
       <c r="F16">
-        <v>1664.978</v>
+        <v>1783.905</v>
       </c>
       <c r="G16">
         <v>354.7</v>
@@ -2605,28 +2605,28 @@
         <v>706.7</v>
       </c>
       <c r="M16">
-        <v>86.24586040000001</v>
+        <v>92.40627900000003</v>
       </c>
       <c r="N16">
-        <v>620.4541396000001</v>
+        <v>614.293721</v>
       </c>
       <c r="O16">
-        <v>62.04541396000001</v>
+        <v>61.4293721</v>
       </c>
       <c r="P16">
-        <v>558.4087256400001</v>
+        <v>552.8643489</v>
       </c>
       <c r="Q16">
-        <v>799.20872564</v>
+        <v>793.6643489</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07818201094147187</v>
+        <v>0.07852974760591913</v>
       </c>
       <c r="T16">
-        <v>0.6490540166898862</v>
+        <v>0.6560239321536842</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.194016463194796</v>
+        <v>7.647748698981807</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07374328546503126</v>
+        <v>0.07372324152039669</v>
       </c>
       <c r="C17">
-        <v>10696.94994082255</v>
+        <v>10586.72737358285</v>
       </c>
       <c r="D17">
-        <v>12126.15494082255</v>
+        <v>12134.85937358285</v>
       </c>
       <c r="E17">
-        <v>-3794.695000000001</v>
+        <v>-3675.768</v>
       </c>
       <c r="F17">
-        <v>1783.905</v>
+        <v>1902.832</v>
       </c>
       <c r="G17">
         <v>354.7</v>
@@ -2687,28 +2687,28 @@
         <v>706.7</v>
       </c>
       <c r="M17">
-        <v>92.406279</v>
+        <v>98.5666976</v>
       </c>
       <c r="N17">
-        <v>614.293721</v>
+        <v>608.1333024</v>
       </c>
       <c r="O17">
-        <v>61.4293721</v>
+        <v>60.81333024000001</v>
       </c>
       <c r="P17">
-        <v>552.8643489</v>
+        <v>547.31997216</v>
       </c>
       <c r="Q17">
-        <v>793.6643489</v>
+        <v>788.1199721600001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07852974760591913</v>
+        <v>0.07888576371475797</v>
       </c>
       <c r="T17">
-        <v>0.6560239321536842</v>
+        <v>0.6631597979856676</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.647748698981808</v>
+        <v>7.169764405295446</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07372324152039669</v>
+        <v>0.07370319757576214</v>
       </c>
       <c r="C18">
-        <v>10586.72737358285</v>
+        <v>10476.51731180371</v>
       </c>
       <c r="D18">
-        <v>12134.85937358285</v>
+        <v>12143.5763118037</v>
       </c>
       <c r="E18">
-        <v>-3675.768</v>
+        <v>-3556.841</v>
       </c>
       <c r="F18">
-        <v>1902.832</v>
+        <v>2021.759</v>
       </c>
       <c r="G18">
         <v>354.7</v>
@@ -2769,28 +2769,28 @@
         <v>706.7</v>
       </c>
       <c r="M18">
-        <v>98.5666976</v>
+        <v>104.7271162</v>
       </c>
       <c r="N18">
-        <v>608.1333024</v>
+        <v>601.9728838000001</v>
       </c>
       <c r="O18">
-        <v>60.81333024000001</v>
+        <v>60.19728838000001</v>
       </c>
       <c r="P18">
-        <v>547.31997216</v>
+        <v>541.7755954200001</v>
       </c>
       <c r="Q18">
-        <v>788.1199721600001</v>
+        <v>782.5755954200001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07888576371475797</v>
+        <v>0.07925035852501464</v>
       </c>
       <c r="T18">
-        <v>0.6631597979856676</v>
+        <v>0.6704676123919158</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.169764405295446</v>
+        <v>6.748013557925125</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07370319757576214</v>
+        <v>0.0739585536311276</v>
       </c>
       <c r="C19">
-        <v>10476.51731180371</v>
+        <v>10247.46619869643</v>
       </c>
       <c r="D19">
-        <v>12143.5763118037</v>
+        <v>12033.45219869643</v>
       </c>
       <c r="E19">
-        <v>-3556.841</v>
+        <v>-3437.914</v>
       </c>
       <c r="F19">
-        <v>2021.759</v>
+        <v>2140.686000000001</v>
       </c>
       <c r="G19">
         <v>354.7</v>
@@ -2851,45 +2851,45 @@
         <v>706.7</v>
       </c>
       <c r="M19">
-        <v>104.7271162</v>
+        <v>114.526701</v>
       </c>
       <c r="N19">
-        <v>601.9728838000001</v>
+        <v>592.173299</v>
       </c>
       <c r="O19">
-        <v>60.19728838000001</v>
+        <v>59.21732990000001</v>
       </c>
       <c r="P19">
-        <v>541.7755954200001</v>
+        <v>532.9559691000001</v>
       </c>
       <c r="Q19">
-        <v>782.5755954200001</v>
+        <v>773.7559691000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07925035852501464</v>
+        <v>0.07962384589161903</v>
       </c>
       <c r="T19">
-        <v>0.6704676123919158</v>
+        <v>0.6779536661739261</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.748013557925125</v>
+        <v>6.170613436250118</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0739585536311276</v>
+        <v>0.07395380968649305</v>
       </c>
       <c r="C20">
-        <v>10247.46619869643</v>
+        <v>10130.56684723241</v>
       </c>
       <c r="D20">
-        <v>12033.45219869643</v>
+        <v>12035.47984723241</v>
       </c>
       <c r="E20">
-        <v>-3437.914</v>
+        <v>-3318.987</v>
       </c>
       <c r="F20">
-        <v>2140.686</v>
+        <v>2259.613</v>
       </c>
       <c r="G20">
         <v>354.7</v>
@@ -2933,28 +2933,28 @@
         <v>706.7</v>
       </c>
       <c r="M20">
-        <v>114.526701</v>
+        <v>120.8892955</v>
       </c>
       <c r="N20">
-        <v>592.173299</v>
+        <v>585.8107045</v>
       </c>
       <c r="O20">
-        <v>59.21732990000001</v>
+        <v>58.58107045000001</v>
       </c>
       <c r="P20">
-        <v>532.9559691000001</v>
+        <v>527.2296340500001</v>
       </c>
       <c r="Q20">
-        <v>773.7559691000001</v>
+        <v>768.0296340500001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07962384589161903</v>
+        <v>0.08000655516850994</v>
       </c>
       <c r="T20">
-        <v>0.6779536661739261</v>
+        <v>0.6856245607900601</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.17061343625012</v>
+        <v>5.845844308026429</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07395380968649305</v>
+        <v>0.07409306574185852</v>
       </c>
       <c r="C21">
-        <v>10130.56684723241</v>
+        <v>9952.402242398495</v>
       </c>
       <c r="D21">
-        <v>12035.47984723241</v>
+        <v>11976.2422423985</v>
       </c>
       <c r="E21">
-        <v>-3318.987</v>
+        <v>-3200.06</v>
       </c>
       <c r="F21">
-        <v>2259.613</v>
+        <v>2378.54</v>
       </c>
       <c r="G21">
         <v>354.7</v>
@@ -3015,45 +3015,45 @@
         <v>706.7</v>
       </c>
       <c r="M21">
-        <v>120.8892955</v>
+        <v>129.154722</v>
       </c>
       <c r="N21">
-        <v>585.8107045</v>
+        <v>577.5452780000001</v>
       </c>
       <c r="O21">
-        <v>58.58107045000001</v>
+        <v>57.75452780000001</v>
       </c>
       <c r="P21">
-        <v>527.2296340500001</v>
+        <v>519.7907502</v>
       </c>
       <c r="Q21">
-        <v>768.0296340500001</v>
+        <v>760.5907502</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08000655516850994</v>
+        <v>0.08039883217732313</v>
       </c>
       <c r="T21">
-        <v>0.6856245607900601</v>
+        <v>0.6934872277715975</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.845844308026429</v>
+        <v>5.471731803967647</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07409306574185852</v>
+        <v>0.07409552179722395</v>
       </c>
       <c r="C22">
-        <v>9952.402242398495</v>
+        <v>9832.435702847752</v>
       </c>
       <c r="D22">
-        <v>11976.2422423985</v>
+        <v>11975.20270284775</v>
       </c>
       <c r="E22">
-        <v>-3200.06</v>
+        <v>-3081.133</v>
       </c>
       <c r="F22">
-        <v>2378.54</v>
+        <v>2497.467000000001</v>
       </c>
       <c r="G22">
         <v>354.7</v>
@@ -3097,28 +3097,28 @@
         <v>706.7</v>
       </c>
       <c r="M22">
-        <v>129.154722</v>
+        <v>135.6124581</v>
       </c>
       <c r="N22">
-        <v>577.5452780000001</v>
+        <v>571.0875419</v>
       </c>
       <c r="O22">
-        <v>57.75452780000001</v>
+        <v>57.10875419000001</v>
       </c>
       <c r="P22">
-        <v>519.7907502</v>
+        <v>513.97878771</v>
       </c>
       <c r="Q22">
-        <v>760.5907502</v>
+        <v>754.77878771</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08039883217732313</v>
+        <v>0.08080104024965057</v>
       </c>
       <c r="T22">
-        <v>0.6934872277715975</v>
+        <v>0.701548949613427</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.471731803967647</v>
+        <v>5.211173146635854</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07409552179722395</v>
+        <v>0.0740979778525894</v>
       </c>
       <c r="C23">
-        <v>9832.435702847752</v>
+        <v>9712.469343745704</v>
       </c>
       <c r="D23">
-        <v>11975.20270284775</v>
+        <v>11974.1633437457</v>
       </c>
       <c r="E23">
-        <v>-3081.133</v>
+        <v>-2962.206</v>
       </c>
       <c r="F23">
-        <v>2497.467</v>
+        <v>2616.394</v>
       </c>
       <c r="G23">
         <v>354.7</v>
@@ -3179,28 +3179,28 @@
         <v>706.7</v>
       </c>
       <c r="M23">
-        <v>135.6124581</v>
+        <v>142.0701942</v>
       </c>
       <c r="N23">
-        <v>571.0875419</v>
+        <v>564.6298058</v>
       </c>
       <c r="O23">
-        <v>57.10875419000001</v>
+        <v>56.46298058</v>
       </c>
       <c r="P23">
-        <v>513.97878771</v>
+        <v>508.16682522</v>
       </c>
       <c r="Q23">
-        <v>754.77878771</v>
+        <v>748.9668252199999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08080104024965057</v>
+        <v>0.08121356134947359</v>
       </c>
       <c r="T23">
-        <v>0.701548949613427</v>
+        <v>0.7098173822717135</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.211173146635855</v>
+        <v>4.974301639970588</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0740979778525894</v>
+        <v>0.07410043390795486</v>
       </c>
       <c r="C24">
-        <v>9712.469343745704</v>
+        <v>9592.503165045373</v>
       </c>
       <c r="D24">
-        <v>11974.1633437457</v>
+        <v>11973.12416504537</v>
       </c>
       <c r="E24">
-        <v>-2962.206</v>
+        <v>-2843.279</v>
       </c>
       <c r="F24">
-        <v>2616.394</v>
+        <v>2735.321</v>
       </c>
       <c r="G24">
         <v>354.7</v>
@@ -3261,28 +3261,28 @@
         <v>706.7</v>
       </c>
       <c r="M24">
-        <v>142.0701942</v>
+        <v>148.5279303</v>
       </c>
       <c r="N24">
-        <v>564.6298058</v>
+        <v>558.1720697000001</v>
       </c>
       <c r="O24">
-        <v>56.46298058</v>
+        <v>55.81720697000001</v>
       </c>
       <c r="P24">
-        <v>508.16682522</v>
+        <v>502.35486273</v>
       </c>
       <c r="Q24">
-        <v>748.9668252199999</v>
+        <v>743.1548627300001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08121356134947359</v>
+        <v>0.08163679728305825</v>
       </c>
       <c r="T24">
-        <v>0.7098173822717135</v>
+        <v>0.7183005794146311</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.974301639970588</v>
+        <v>4.758027655624041</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07410043390795486</v>
+        <v>0.0741028899633203</v>
       </c>
       <c r="C25">
-        <v>9592.503165045373</v>
+        <v>9472.537166699803</v>
       </c>
       <c r="D25">
-        <v>11973.12416504537</v>
+        <v>11972.0851666998</v>
       </c>
       <c r="E25">
-        <v>-2843.279</v>
+        <v>-2724.352</v>
       </c>
       <c r="F25">
-        <v>2735.321</v>
+        <v>2854.248000000001</v>
       </c>
       <c r="G25">
         <v>354.7</v>
@@ -3343,28 +3343,28 @@
         <v>706.7</v>
       </c>
       <c r="M25">
-        <v>148.5279303</v>
+        <v>154.9856664</v>
       </c>
       <c r="N25">
-        <v>558.1720697000001</v>
+        <v>551.7143336</v>
       </c>
       <c r="O25">
-        <v>55.81720697000001</v>
+        <v>55.17143336000001</v>
       </c>
       <c r="P25">
-        <v>502.35486273</v>
+        <v>496.54290024</v>
       </c>
       <c r="Q25">
-        <v>743.1548627300001</v>
+        <v>737.3429002400001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08163679728305825</v>
+        <v>0.08207117100436882</v>
       </c>
       <c r="T25">
-        <v>0.7183005794146311</v>
+        <v>0.7270070185876253</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.758027655624041</v>
+        <v>4.559776503306372</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0741028899633203</v>
+        <v>0.07410534601868576</v>
       </c>
       <c r="C26">
-        <v>9472.537166699805</v>
+        <v>9352.571348662037</v>
       </c>
       <c r="D26">
-        <v>11972.0851666998</v>
+        <v>11971.04634866204</v>
       </c>
       <c r="E26">
-        <v>-2724.352</v>
+        <v>-2605.425</v>
       </c>
       <c r="F26">
-        <v>2854.248</v>
+        <v>2973.175</v>
       </c>
       <c r="G26">
         <v>354.7</v>
@@ -3425,28 +3425,28 @@
         <v>706.7</v>
       </c>
       <c r="M26">
-        <v>154.9856664</v>
+        <v>161.4434025</v>
       </c>
       <c r="N26">
-        <v>551.7143336</v>
+        <v>545.2565975</v>
       </c>
       <c r="O26">
-        <v>55.17143336000001</v>
+        <v>54.52565975</v>
       </c>
       <c r="P26">
-        <v>496.54290024</v>
+        <v>490.73093775</v>
       </c>
       <c r="Q26">
-        <v>737.3429002400001</v>
+        <v>731.53093775</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08207117100436882</v>
+        <v>0.08251712802491434</v>
       </c>
       <c r="T26">
-        <v>0.7270070185876253</v>
+        <v>0.7359456294718995</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.559776503306373</v>
+        <v>4.377385443174118</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07410534601868576</v>
+        <v>0.07434180207405121</v>
       </c>
       <c r="C27">
-        <v>9352.571348662037</v>
+        <v>9134.469587697136</v>
       </c>
       <c r="D27">
-        <v>11971.04634866204</v>
+        <v>11871.87158769714</v>
       </c>
       <c r="E27">
-        <v>-2605.425</v>
+        <v>-2486.498</v>
       </c>
       <c r="F27">
-        <v>2973.175</v>
+        <v>3092.102</v>
       </c>
       <c r="G27">
         <v>354.7</v>
@@ -3507,45 +3507,45 @@
         <v>706.7</v>
       </c>
       <c r="M27">
-        <v>161.4434025</v>
+        <v>170.9932406</v>
       </c>
       <c r="N27">
-        <v>545.2565975</v>
+        <v>535.7067594</v>
       </c>
       <c r="O27">
-        <v>54.52565975</v>
+        <v>53.57067594</v>
       </c>
       <c r="P27">
-        <v>490.73093775</v>
+        <v>482.13608346</v>
       </c>
       <c r="Q27">
-        <v>731.53093775</v>
+        <v>722.93608346</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08251712802491434</v>
+        <v>0.08297513793790703</v>
       </c>
       <c r="T27">
-        <v>0.7359456294718995</v>
+        <v>0.7451258244341269</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.1</v>
       </c>
       <c r="W27">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.377385443174118</v>
+        <v>4.13291190646047</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07434180207405121</v>
+        <v>0.07435325812941666</v>
       </c>
       <c r="C28">
-        <v>9134.469587697136</v>
+        <v>9010.779389830757</v>
       </c>
       <c r="D28">
-        <v>11871.87158769714</v>
+        <v>11867.10838983076</v>
       </c>
       <c r="E28">
-        <v>-2486.498</v>
+        <v>-2367.571</v>
       </c>
       <c r="F28">
-        <v>3092.102</v>
+        <v>3211.029</v>
       </c>
       <c r="G28">
         <v>354.7</v>
@@ -3589,28 +3589,28 @@
         <v>706.7</v>
       </c>
       <c r="M28">
-        <v>170.9932406</v>
+        <v>177.5699037</v>
       </c>
       <c r="N28">
-        <v>535.7067594</v>
+        <v>529.1300963</v>
       </c>
       <c r="O28">
-        <v>53.57067594</v>
+        <v>52.91300963</v>
       </c>
       <c r="P28">
-        <v>482.13608346</v>
+        <v>476.21708667</v>
       </c>
       <c r="Q28">
-        <v>722.93608346</v>
+        <v>717.01708667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08297513793790703</v>
+        <v>0.08344569606769406</v>
       </c>
       <c r="T28">
-        <v>0.7451258244341269</v>
+        <v>0.7545575315871003</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.13291190646047</v>
+        <v>3.979841095110082</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07435325812941666</v>
+        <v>0.0743647141847821</v>
       </c>
       <c r="C29">
-        <v>9010.779389830757</v>
+        <v>8887.093012584335</v>
       </c>
       <c r="D29">
-        <v>11867.10838983076</v>
+        <v>11862.34901258433</v>
       </c>
       <c r="E29">
-        <v>-2367.571</v>
+        <v>-2248.644</v>
       </c>
       <c r="F29">
-        <v>3211.029</v>
+        <v>3329.956000000001</v>
       </c>
       <c r="G29">
         <v>354.7</v>
@@ -3671,28 +3671,28 @@
         <v>706.7</v>
       </c>
       <c r="M29">
-        <v>177.5699037</v>
+        <v>184.1465668</v>
       </c>
       <c r="N29">
-        <v>529.1300963</v>
+        <v>522.5534332</v>
       </c>
       <c r="O29">
-        <v>52.91300963</v>
+        <v>52.25534332</v>
       </c>
       <c r="P29">
-        <v>476.21708667</v>
+        <v>470.29808988</v>
       </c>
       <c r="Q29">
-        <v>717.01708667</v>
+        <v>711.09808988</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08344569606769406</v>
+        <v>0.08392932525664182</v>
       </c>
       <c r="T29">
-        <v>0.7545575315871003</v>
+        <v>0.764251230605434</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.979841095110082</v>
+        <v>3.837703913141865</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0743647141847821</v>
+        <v>0.07437617024014756</v>
       </c>
       <c r="C30">
-        <v>8887.093012584335</v>
+        <v>8763.410451362852</v>
       </c>
       <c r="D30">
-        <v>11862.34901258433</v>
+        <v>11857.59345136285</v>
       </c>
       <c r="E30">
-        <v>-2248.644</v>
+        <v>-2129.717</v>
       </c>
       <c r="F30">
-        <v>3329.956000000001</v>
+        <v>3448.883000000001</v>
       </c>
       <c r="G30">
         <v>354.7</v>
@@ -3753,28 +3753,28 @@
         <v>706.7</v>
       </c>
       <c r="M30">
-        <v>184.1465668</v>
+        <v>190.7232299</v>
       </c>
       <c r="N30">
-        <v>522.5534332</v>
+        <v>515.9767701000001</v>
       </c>
       <c r="O30">
-        <v>52.25534332</v>
+        <v>51.59767701000001</v>
       </c>
       <c r="P30">
-        <v>470.29808988</v>
+        <v>464.3790930900001</v>
       </c>
       <c r="Q30">
-        <v>711.09808988</v>
+        <v>705.1790930900002</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08392932525664182</v>
+        <v>0.08442657780302473</v>
       </c>
       <c r="T30">
-        <v>0.764251230605434</v>
+        <v>0.7742179915679462</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.837703913141865</v>
+        <v>3.705369295447319</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07437617024014756</v>
+        <v>0.074387626295513</v>
       </c>
       <c r="C31">
-        <v>8763.410451362854</v>
+        <v>8639.731701578681</v>
       </c>
       <c r="D31">
-        <v>11857.59345136285</v>
+        <v>11852.84170157868</v>
       </c>
       <c r="E31">
-        <v>-2129.717000000001</v>
+        <v>-2010.79</v>
       </c>
       <c r="F31">
-        <v>3448.883</v>
+        <v>3567.81</v>
       </c>
       <c r="G31">
         <v>354.7</v>
@@ -3835,28 +3835,28 @@
         <v>706.7</v>
       </c>
       <c r="M31">
-        <v>190.7232299</v>
+        <v>197.299893</v>
       </c>
       <c r="N31">
-        <v>515.9767701000001</v>
+        <v>509.400107</v>
       </c>
       <c r="O31">
-        <v>51.59767701000001</v>
+        <v>50.94001070000001</v>
       </c>
       <c r="P31">
-        <v>464.3790930900001</v>
+        <v>458.4600963</v>
       </c>
       <c r="Q31">
-        <v>705.1790930900002</v>
+        <v>699.2600963</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08442657780302473</v>
+        <v>0.08493803756501858</v>
       </c>
       <c r="T31">
-        <v>0.7742179915679461</v>
+        <v>0.7844695171293872</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.705369295447319</v>
+        <v>3.581856985599075</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.074387626295513</v>
+        <v>0.07439908235087846</v>
       </c>
       <c r="C32">
-        <v>8639.731701578681</v>
+        <v>8516.056758651517</v>
       </c>
       <c r="D32">
-        <v>11852.84170157868</v>
+        <v>11848.09375865152</v>
       </c>
       <c r="E32">
-        <v>-2010.79</v>
+        <v>-1891.863</v>
       </c>
       <c r="F32">
-        <v>3567.81</v>
+        <v>3686.737</v>
       </c>
       <c r="G32">
         <v>354.7</v>
@@ -3917,28 +3917,28 @@
         <v>706.7</v>
       </c>
       <c r="M32">
-        <v>197.299893</v>
+        <v>203.8765561</v>
       </c>
       <c r="N32">
-        <v>509.400107</v>
+        <v>502.8234439</v>
       </c>
       <c r="O32">
-        <v>50.94001070000001</v>
+        <v>50.28234439000001</v>
       </c>
       <c r="P32">
-        <v>458.4600963</v>
+        <v>452.54109951</v>
       </c>
       <c r="Q32">
-        <v>699.2600963</v>
+        <v>693.34109951</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08493803756501858</v>
+        <v>0.08546432224764994</v>
       </c>
       <c r="T32">
-        <v>0.7844695171293872</v>
+        <v>0.795018188359276</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.581856985599075</v>
+        <v>3.466313211870072</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07439908235087846</v>
+        <v>0.0744105384062439</v>
       </c>
       <c r="C33">
-        <v>8516.056758651517</v>
+        <v>8392.385618008415</v>
       </c>
       <c r="D33">
-        <v>11848.09375865152</v>
+        <v>11843.34961800841</v>
       </c>
       <c r="E33">
-        <v>-1891.863</v>
+        <v>-1772.936</v>
       </c>
       <c r="F33">
-        <v>3686.737</v>
+        <v>3805.664</v>
       </c>
       <c r="G33">
         <v>354.7</v>
@@ -3999,28 +3999,28 @@
         <v>706.7</v>
       </c>
       <c r="M33">
-        <v>203.8765561</v>
+        <v>210.4532192</v>
       </c>
       <c r="N33">
-        <v>502.8234439</v>
+        <v>496.2467808</v>
       </c>
       <c r="O33">
-        <v>50.28234439000001</v>
+        <v>49.62467808</v>
       </c>
       <c r="P33">
-        <v>452.54109951</v>
+        <v>446.62210272</v>
       </c>
       <c r="Q33">
-        <v>693.34109951</v>
+        <v>687.42210272</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08546432224764994</v>
+        <v>0.08600608589153516</v>
       </c>
       <c r="T33">
-        <v>0.795018188359276</v>
+        <v>0.8058771146253378</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.466313211870072</v>
+        <v>3.357990923999133</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0744105384062439</v>
+        <v>0.07442199446160935</v>
       </c>
       <c r="C34">
-        <v>8392.385618008415</v>
+        <v>8268.718275083733</v>
       </c>
       <c r="D34">
-        <v>11843.34961800841</v>
+        <v>11838.60927508373</v>
       </c>
       <c r="E34">
-        <v>-1772.936</v>
+        <v>-1654.009</v>
       </c>
       <c r="F34">
-        <v>3805.664</v>
+        <v>3924.591</v>
       </c>
       <c r="G34">
         <v>354.7</v>
@@ -4081,28 +4081,28 @@
         <v>706.7</v>
       </c>
       <c r="M34">
-        <v>210.4532192</v>
+        <v>217.0298823</v>
       </c>
       <c r="N34">
-        <v>496.2467808</v>
+        <v>489.6701177</v>
       </c>
       <c r="O34">
-        <v>49.62467808</v>
+        <v>48.96701177</v>
       </c>
       <c r="P34">
-        <v>446.62210272</v>
+        <v>440.70310593</v>
       </c>
       <c r="Q34">
-        <v>687.42210272</v>
+        <v>681.5031059299999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08600608589153516</v>
+        <v>0.08656402158449159</v>
       </c>
       <c r="T34">
-        <v>0.8058771146253378</v>
+        <v>0.8170601879441179</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.357990923999133</v>
+        <v>3.256233623271886</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07442199446160935</v>
+        <v>0.07443345051697481</v>
       </c>
       <c r="C35">
-        <v>8268.718275083733</v>
+        <v>8145.054725319153</v>
       </c>
       <c r="D35">
-        <v>11838.60927508373</v>
+        <v>11833.87272531915</v>
       </c>
       <c r="E35">
-        <v>-1654.009</v>
+        <v>-1535.082</v>
       </c>
       <c r="F35">
-        <v>3924.591</v>
+        <v>4043.518</v>
       </c>
       <c r="G35">
         <v>354.7</v>
@@ -4163,28 +4163,28 @@
         <v>706.7</v>
       </c>
       <c r="M35">
-        <v>217.0298823</v>
+        <v>223.6065454</v>
       </c>
       <c r="N35">
-        <v>489.6701177</v>
+        <v>483.0934546</v>
       </c>
       <c r="O35">
-        <v>48.96701177</v>
+        <v>48.30934546</v>
       </c>
       <c r="P35">
-        <v>440.70310593</v>
+        <v>434.7841091399999</v>
       </c>
       <c r="Q35">
-        <v>681.5031059299999</v>
+        <v>675.58410914</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08656402158449159</v>
+        <v>0.08713886441965882</v>
       </c>
       <c r="T35">
-        <v>0.8170601879441179</v>
+        <v>0.8285821422725581</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.256233623271886</v>
+        <v>3.16046204611683</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07443345051697481</v>
+        <v>0.07444490657234026</v>
       </c>
       <c r="C36">
-        <v>8145.054725319153</v>
+        <v>8021.394964163635</v>
       </c>
       <c r="D36">
-        <v>11833.87272531915</v>
+        <v>11829.13996416363</v>
       </c>
       <c r="E36">
-        <v>-1535.082</v>
+        <v>-1416.155</v>
       </c>
       <c r="F36">
-        <v>4043.518</v>
+        <v>4162.445000000001</v>
       </c>
       <c r="G36">
         <v>354.7</v>
@@ -4245,28 +4245,28 @@
         <v>706.7</v>
       </c>
       <c r="M36">
-        <v>223.6065454</v>
+        <v>230.1832085</v>
       </c>
       <c r="N36">
-        <v>483.0934546</v>
+        <v>476.5167915</v>
       </c>
       <c r="O36">
-        <v>48.30934546</v>
+        <v>47.65167915000001</v>
       </c>
       <c r="P36">
-        <v>434.7841091399999</v>
+        <v>428.86511235</v>
       </c>
       <c r="Q36">
-        <v>675.58410914</v>
+        <v>669.6651123500001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08713886441965882</v>
+        <v>0.08773139472667733</v>
       </c>
       <c r="T36">
-        <v>0.8285821422725581</v>
+        <v>0.8404586182726426</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.16046204611683</v>
+        <v>3.070163130513492</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07444490657234026</v>
+        <v>0.07526636262770571</v>
       </c>
       <c r="C37">
-        <v>8021.394964163635</v>
+        <v>7572.698091441334</v>
       </c>
       <c r="D37">
-        <v>11829.13996416363</v>
+        <v>11499.37009144133</v>
       </c>
       <c r="E37">
-        <v>-1416.155</v>
+        <v>-1297.227999999999</v>
       </c>
       <c r="F37">
-        <v>4162.445000000001</v>
+        <v>4281.372000000001</v>
       </c>
       <c r="G37">
         <v>354.7</v>
@@ -4327,45 +4327,45 @@
         <v>706.7</v>
       </c>
       <c r="M37">
-        <v>230.1832085</v>
+        <v>247.4633016000001</v>
       </c>
       <c r="N37">
-        <v>476.5167915</v>
+        <v>459.2366984</v>
       </c>
       <c r="O37">
-        <v>47.65167915000001</v>
+        <v>45.92366984</v>
       </c>
       <c r="P37">
-        <v>428.86511235</v>
+        <v>413.31302856</v>
       </c>
       <c r="Q37">
-        <v>669.6651123500001</v>
+        <v>654.11302856</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08773139472667733</v>
+        <v>0.08834244160579019</v>
       </c>
       <c r="T37">
-        <v>0.8404586182726426</v>
+        <v>0.8527062341477296</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.1</v>
       </c>
       <c r="W37">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.070163130513492</v>
+        <v>2.855776979579423</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07526636262770572</v>
+        <v>0.07530031868307116</v>
       </c>
       <c r="C38">
-        <v>7572.69809144133</v>
+        <v>7440.53485315904</v>
       </c>
       <c r="D38">
-        <v>11499.37009144133</v>
+        <v>11486.13385315904</v>
       </c>
       <c r="E38">
-        <v>-1297.228</v>
+        <v>-1178.301</v>
       </c>
       <c r="F38">
-        <v>4281.372</v>
+        <v>4400.299</v>
       </c>
       <c r="G38">
         <v>354.7</v>
@@ -4409,28 +4409,28 @@
         <v>706.7</v>
       </c>
       <c r="M38">
-        <v>247.4633016</v>
+        <v>254.3372822</v>
       </c>
       <c r="N38">
-        <v>459.2366984</v>
+        <v>452.3627178</v>
       </c>
       <c r="O38">
-        <v>45.92366984</v>
+        <v>45.23627178000001</v>
       </c>
       <c r="P38">
-        <v>413.31302856</v>
+        <v>407.12644602</v>
       </c>
       <c r="Q38">
-        <v>654.11302856</v>
+        <v>647.92644602</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08834244160579019</v>
+        <v>0.08897288679852565</v>
       </c>
       <c r="T38">
-        <v>0.8527062341477296</v>
+        <v>0.8653426632252003</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.855776979579423</v>
+        <v>2.778593817969169</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07530031868307116</v>
+        <v>0.07533427473843662</v>
       </c>
       <c r="C39">
-        <v>7440.53485315904</v>
+        <v>7308.40205073094</v>
       </c>
       <c r="D39">
-        <v>11486.13385315904</v>
+        <v>11472.92805073094</v>
       </c>
       <c r="E39">
-        <v>-1178.301</v>
+        <v>-1059.374</v>
       </c>
       <c r="F39">
-        <v>4400.299</v>
+        <v>4519.226000000001</v>
       </c>
       <c r="G39">
         <v>354.7</v>
@@ -4491,28 +4491,28 @@
         <v>706.7</v>
       </c>
       <c r="M39">
-        <v>254.3372822</v>
+        <v>261.2112628</v>
       </c>
       <c r="N39">
-        <v>452.3627178</v>
+        <v>445.4887372</v>
       </c>
       <c r="O39">
-        <v>45.23627178000001</v>
+        <v>44.54887372</v>
       </c>
       <c r="P39">
-        <v>407.12644602</v>
+        <v>400.93986348</v>
       </c>
       <c r="Q39">
-        <v>647.92644602</v>
+        <v>641.7398634799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08897288679852565</v>
+        <v>0.08962366893296228</v>
       </c>
       <c r="T39">
-        <v>0.8653426632252003</v>
+        <v>0.8783867190471057</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.778593817969169</v>
+        <v>2.705472928022612</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07533427473843662</v>
+        <v>0.07536823079380206</v>
       </c>
       <c r="C40">
-        <v>7308.40205073094</v>
+        <v>7176.299579299761</v>
       </c>
       <c r="D40">
-        <v>11472.92805073094</v>
+        <v>11459.75257929976</v>
       </c>
       <c r="E40">
-        <v>-1059.374</v>
+        <v>-940.4470000000001</v>
       </c>
       <c r="F40">
-        <v>4519.226000000001</v>
+        <v>4638.153</v>
       </c>
       <c r="G40">
         <v>354.7</v>
@@ -4573,28 +4573,28 @@
         <v>706.7</v>
       </c>
       <c r="M40">
-        <v>261.2112628</v>
+        <v>268.0852434</v>
       </c>
       <c r="N40">
-        <v>445.4887372</v>
+        <v>438.6147566</v>
       </c>
       <c r="O40">
-        <v>44.54887372</v>
+        <v>43.86147566</v>
       </c>
       <c r="P40">
-        <v>400.93986348</v>
+        <v>394.75328094</v>
       </c>
       <c r="Q40">
-        <v>641.7398634799999</v>
+        <v>635.55328094</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08962366893296228</v>
+        <v>0.09029578818656075</v>
       </c>
       <c r="T40">
-        <v>0.8783867190471057</v>
+        <v>0.891858448830385</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.705472928022612</v>
+        <v>2.636101827304083</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07536823079380206</v>
+        <v>0.07540218684916751</v>
       </c>
       <c r="C41">
-        <v>7176.299579299761</v>
+        <v>7044.227334489308</v>
       </c>
       <c r="D41">
-        <v>11459.75257929976</v>
+        <v>11446.60733448931</v>
       </c>
       <c r="E41">
-        <v>-940.4470000000001</v>
+        <v>-821.5199999999995</v>
       </c>
       <c r="F41">
-        <v>4638.153</v>
+        <v>4757.080000000001</v>
       </c>
       <c r="G41">
         <v>354.7</v>
@@ -4655,28 +4655,28 @@
         <v>706.7</v>
       </c>
       <c r="M41">
-        <v>268.0852434</v>
+        <v>274.9592240000001</v>
       </c>
       <c r="N41">
-        <v>438.6147566</v>
+        <v>431.740776</v>
       </c>
       <c r="O41">
-        <v>43.86147566</v>
+        <v>43.1740776</v>
       </c>
       <c r="P41">
-        <v>394.75328094</v>
+        <v>388.5666984</v>
       </c>
       <c r="Q41">
-        <v>635.55328094</v>
+        <v>629.3666983999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09029578818656075</v>
+        <v>0.09099031141527919</v>
       </c>
       <c r="T41">
-        <v>0.891858448830385</v>
+        <v>0.905779236273107</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.636101827304083</v>
+        <v>2.570199281621481</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07540218684916751</v>
+        <v>0.07543614290453297</v>
       </c>
       <c r="C42">
-        <v>7044.227334489308</v>
+        <v>6912.185212401771</v>
       </c>
       <c r="D42">
-        <v>11446.60733448931</v>
+        <v>11433.49221240177</v>
       </c>
       <c r="E42">
-        <v>-821.5199999999995</v>
+        <v>-702.5929999999998</v>
       </c>
       <c r="F42">
-        <v>4757.080000000001</v>
+        <v>4876.007000000001</v>
       </c>
       <c r="G42">
         <v>354.7</v>
@@ -4737,28 +4737,28 @@
         <v>706.7</v>
       </c>
       <c r="M42">
-        <v>274.9592240000001</v>
+        <v>281.8332046</v>
       </c>
       <c r="N42">
-        <v>431.740776</v>
+        <v>424.8667954</v>
       </c>
       <c r="O42">
-        <v>43.1740776</v>
+        <v>42.48667954</v>
       </c>
       <c r="P42">
-        <v>388.5666984</v>
+        <v>382.38011586</v>
       </c>
       <c r="Q42">
-        <v>629.3666983999999</v>
+        <v>623.18011586</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09099031141527919</v>
+        <v>0.09170837780429317</v>
       </c>
       <c r="T42">
-        <v>0.905779236273107</v>
+        <v>0.9201719148155821</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.570199281621481</v>
+        <v>2.50751149426486</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07543614290453297</v>
+        <v>0.07679309895989841</v>
       </c>
       <c r="C43">
-        <v>6912.185212401771</v>
+        <v>6292.671081322476</v>
       </c>
       <c r="D43">
-        <v>11433.49221240177</v>
+        <v>10932.90508132248</v>
       </c>
       <c r="E43">
-        <v>-702.5929999999998</v>
+        <v>-583.6659999999993</v>
       </c>
       <c r="F43">
-        <v>4876.007000000001</v>
+        <v>4994.934000000001</v>
       </c>
       <c r="G43">
         <v>354.7</v>
@@ -4819,45 +4819,45 @@
         <v>706.7</v>
       </c>
       <c r="M43">
-        <v>281.8332046</v>
+        <v>306.1894542000001</v>
       </c>
       <c r="N43">
-        <v>424.8667954</v>
+        <v>400.5105458</v>
       </c>
       <c r="O43">
-        <v>42.48667954</v>
+        <v>40.05105458</v>
       </c>
       <c r="P43">
-        <v>382.38011586</v>
+        <v>360.45949122</v>
       </c>
       <c r="Q43">
-        <v>623.18011586</v>
+        <v>601.25949122</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09170837780429317</v>
+        <v>0.09245120510327313</v>
       </c>
       <c r="T43">
-        <v>0.9201719148155821</v>
+        <v>0.9350608926181427</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.1</v>
       </c>
       <c r="W43">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.50751149426486</v>
+        <v>2.308048139170692</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07679309895989841</v>
+        <v>0.07685855501526387</v>
       </c>
       <c r="C44">
-        <v>6292.671081322477</v>
+        <v>6150.702930826049</v>
       </c>
       <c r="D44">
-        <v>10932.90508132248</v>
+        <v>10909.86393082605</v>
       </c>
       <c r="E44">
-        <v>-583.6660000000002</v>
+        <v>-464.7390000000005</v>
       </c>
       <c r="F44">
-        <v>4994.934</v>
+        <v>5113.861</v>
       </c>
       <c r="G44">
         <v>354.7</v>
@@ -4901,28 +4901,28 @@
         <v>706.7</v>
       </c>
       <c r="M44">
-        <v>306.1894542</v>
+        <v>313.4796793</v>
       </c>
       <c r="N44">
-        <v>400.5105458</v>
+        <v>393.2203207000001</v>
       </c>
       <c r="O44">
-        <v>40.05105458000001</v>
+        <v>39.32203207000001</v>
       </c>
       <c r="P44">
-        <v>360.45949122</v>
+        <v>353.89828863</v>
       </c>
       <c r="Q44">
-        <v>601.25949122</v>
+        <v>594.69828863</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09245120510327312</v>
+        <v>0.09322009651800678</v>
       </c>
       <c r="T44">
-        <v>0.9350608926181426</v>
+        <v>0.9504722906944773</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.308048139170693</v>
+        <v>2.254372601050444</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07685855501526387</v>
+        <v>0.07803281107062933</v>
       </c>
       <c r="C45">
-        <v>6150.702930826049</v>
+        <v>5634.324596038214</v>
       </c>
       <c r="D45">
-        <v>10909.86393082605</v>
+        <v>10512.41259603821</v>
       </c>
       <c r="E45">
-        <v>-464.7390000000005</v>
+        <v>-345.8119999999999</v>
       </c>
       <c r="F45">
-        <v>5113.861</v>
+        <v>5232.788</v>
       </c>
       <c r="G45">
         <v>354.7</v>
@@ -4983,45 +4983,45 @@
         <v>706.7</v>
       </c>
       <c r="M45">
-        <v>313.4796793</v>
+        <v>335.4217108</v>
       </c>
       <c r="N45">
-        <v>393.2203207000001</v>
+        <v>371.2782892</v>
       </c>
       <c r="O45">
-        <v>39.32203207000001</v>
+        <v>37.12782892000001</v>
       </c>
       <c r="P45">
-        <v>353.89828863</v>
+        <v>334.15046028</v>
       </c>
       <c r="Q45">
-        <v>594.69828863</v>
+        <v>574.95046028</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09322009651800678</v>
+        <v>0.09401644834040951</v>
       </c>
       <c r="T45">
-        <v>0.9504722906944773</v>
+        <v>0.9664340958449669</v>
       </c>
       <c r="U45">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.1</v>
       </c>
       <c r="W45">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.254372601050444</v>
+        <v>2.106899992592846</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07803281107062933</v>
+        <v>0.07812346712599477</v>
       </c>
       <c r="C46">
-        <v>5634.324596038214</v>
+        <v>5485.913943971558</v>
       </c>
       <c r="D46">
-        <v>10512.41259603821</v>
+        <v>10482.92894397156</v>
       </c>
       <c r="E46">
-        <v>-345.8119999999999</v>
+        <v>-226.8850000000002</v>
       </c>
       <c r="F46">
-        <v>5232.788</v>
+        <v>5351.715</v>
       </c>
       <c r="G46">
         <v>354.7</v>
@@ -5065,28 +5065,28 @@
         <v>706.7</v>
       </c>
       <c r="M46">
-        <v>335.4217108</v>
+        <v>343.0449315</v>
       </c>
       <c r="N46">
-        <v>371.2782892</v>
+        <v>363.6550685</v>
       </c>
       <c r="O46">
-        <v>37.12782892000001</v>
+        <v>36.36550685</v>
       </c>
       <c r="P46">
-        <v>334.15046028</v>
+        <v>327.28956165</v>
       </c>
       <c r="Q46">
-        <v>574.95046028</v>
+        <v>568.08956165</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09401644834040951</v>
+        <v>0.09484175841089958</v>
       </c>
       <c r="T46">
-        <v>0.9664340958449669</v>
+        <v>0.9829763302736558</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.106899992592846</v>
+        <v>2.06007999275745</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07812346712599477</v>
+        <v>0.07821412318136023</v>
       </c>
       <c r="C47">
-        <v>5485.913943971558</v>
+        <v>5337.668212089792</v>
       </c>
       <c r="D47">
-        <v>10482.92894397156</v>
+        <v>10453.61021208979</v>
       </c>
       <c r="E47">
-        <v>-226.8850000000002</v>
+        <v>-107.9579999999996</v>
       </c>
       <c r="F47">
-        <v>5351.715</v>
+        <v>5470.642000000001</v>
       </c>
       <c r="G47">
         <v>354.7</v>
@@ -5147,28 +5147,28 @@
         <v>706.7</v>
       </c>
       <c r="M47">
-        <v>343.0449315</v>
+        <v>350.6681522000001</v>
       </c>
       <c r="N47">
-        <v>363.6550685</v>
+        <v>356.0318478</v>
       </c>
       <c r="O47">
-        <v>36.36550685</v>
+        <v>35.60318478</v>
       </c>
       <c r="P47">
-        <v>327.28956165</v>
+        <v>320.42866302</v>
       </c>
       <c r="Q47">
-        <v>568.08956165</v>
+        <v>561.22866302</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09484175841089958</v>
+        <v>0.09569763552103744</v>
       </c>
       <c r="T47">
-        <v>0.9829763302736558</v>
+        <v>1.000131240051556</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.06007999275745</v>
+        <v>2.01529564508881</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07821412318136023</v>
+        <v>0.08160417923672567</v>
       </c>
       <c r="C48">
-        <v>5337.668212089792</v>
+        <v>4228.959422494275</v>
       </c>
       <c r="D48">
-        <v>10453.61021208979</v>
+        <v>9463.828422494274</v>
       </c>
       <c r="E48">
-        <v>-107.9579999999996</v>
+        <v>10.96900000000005</v>
       </c>
       <c r="F48">
-        <v>5470.642000000001</v>
+        <v>5589.569</v>
       </c>
       <c r="G48">
         <v>354.7</v>
@@ -5229,45 +5229,45 @@
         <v>706.7</v>
       </c>
       <c r="M48">
-        <v>350.6681522000001</v>
+        <v>401.8900111</v>
       </c>
       <c r="N48">
-        <v>356.0318478</v>
+        <v>304.8099889</v>
       </c>
       <c r="O48">
-        <v>35.60318478</v>
+        <v>30.48099889</v>
       </c>
       <c r="P48">
-        <v>320.42866302</v>
+        <v>274.32899001</v>
       </c>
       <c r="Q48">
-        <v>561.22866302</v>
+        <v>515.1289900100001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09569763552103744</v>
+        <v>0.09658580988061446</v>
       </c>
       <c r="T48">
-        <v>1.000131240051556</v>
+        <v>1.017933504915414</v>
       </c>
       <c r="U48">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V48">
         <v>0.1</v>
       </c>
       <c r="W48">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.01529564508881</v>
+        <v>1.758441315985223</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08160417923672567</v>
+        <v>0.08344983529209113</v>
       </c>
       <c r="C49">
-        <v>4228.959422494275</v>
+        <v>3646.100187481668</v>
       </c>
       <c r="D49">
-        <v>9463.828422494274</v>
+        <v>8999.896187481669</v>
       </c>
       <c r="E49">
-        <v>10.96900000000005</v>
+        <v>129.8960000000006</v>
       </c>
       <c r="F49">
-        <v>5589.569</v>
+        <v>5708.496000000001</v>
       </c>
       <c r="G49">
         <v>354.7</v>
@@ -5311,45 +5311,45 @@
         <v>706.7</v>
       </c>
       <c r="M49">
-        <v>401.8900111</v>
+        <v>432.7039968000001</v>
       </c>
       <c r="N49">
-        <v>304.8099889</v>
+        <v>273.9960032</v>
       </c>
       <c r="O49">
-        <v>30.48099889</v>
+        <v>27.39960032</v>
       </c>
       <c r="P49">
-        <v>274.32899001</v>
+        <v>246.59640288</v>
       </c>
       <c r="Q49">
-        <v>515.1289900100001</v>
+        <v>487.39640288</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09658580988061446</v>
+        <v>0.09750814479248293</v>
       </c>
       <c r="T49">
-        <v>1.017933504915414</v>
+        <v>1.036420472274036</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.1</v>
       </c>
       <c r="W49">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.758441315985223</v>
+        <v>1.633218101118311</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08344983529209112</v>
+        <v>0.08364579134745657</v>
       </c>
       <c r="C50">
-        <v>3646.100187481673</v>
+        <v>3480.573972805294</v>
       </c>
       <c r="D50">
-        <v>8999.896187481672</v>
+        <v>8953.296972805294</v>
       </c>
       <c r="E50">
-        <v>129.8959999999997</v>
+        <v>248.8230000000003</v>
       </c>
       <c r="F50">
-        <v>5708.496</v>
+        <v>5827.423000000001</v>
       </c>
       <c r="G50">
         <v>354.7</v>
@@ -5393,28 +5393,28 @@
         <v>706.7</v>
       </c>
       <c r="M50">
-        <v>432.7039968</v>
+        <v>441.7186634000001</v>
       </c>
       <c r="N50">
-        <v>273.9960032</v>
+        <v>264.9813366</v>
       </c>
       <c r="O50">
-        <v>27.39960032</v>
+        <v>26.49813366</v>
       </c>
       <c r="P50">
-        <v>246.59640288</v>
+        <v>238.48320294</v>
       </c>
       <c r="Q50">
-        <v>487.39640288</v>
+        <v>479.28320294</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09750814479248292</v>
+        <v>0.09846664970089525</v>
       </c>
       <c r="T50">
-        <v>1.036420472274036</v>
+        <v>1.055632418744761</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.633218101118312</v>
+        <v>1.599887119462836</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08364579134745657</v>
+        <v>0.08384174740282202</v>
       </c>
       <c r="C51">
-        <v>3480.573972805294</v>
+        <v>3315.52783062372</v>
       </c>
       <c r="D51">
-        <v>8953.296972805294</v>
+        <v>8907.177830623719</v>
       </c>
       <c r="E51">
-        <v>248.8230000000003</v>
+        <v>367.75</v>
       </c>
       <c r="F51">
-        <v>5827.423000000001</v>
+        <v>5946.35</v>
       </c>
       <c r="G51">
         <v>354.7</v>
@@ -5475,28 +5475,28 @@
         <v>706.7</v>
       </c>
       <c r="M51">
-        <v>441.7186634000001</v>
+        <v>450.7333300000001</v>
       </c>
       <c r="N51">
-        <v>264.9813366</v>
+        <v>255.96667</v>
       </c>
       <c r="O51">
-        <v>26.49813366</v>
+        <v>25.596667</v>
       </c>
       <c r="P51">
-        <v>238.48320294</v>
+        <v>230.370003</v>
       </c>
       <c r="Q51">
-        <v>479.28320294</v>
+        <v>471.170003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09846664970089525</v>
+        <v>0.09946349480564404</v>
       </c>
       <c r="T51">
-        <v>1.055632418744761</v>
+        <v>1.075612843074314</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.599887119462836</v>
+        <v>1.567889377073579</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08384174740282202</v>
+        <v>0.08403770345818747</v>
       </c>
       <c r="C52">
-        <v>3315.52783062372</v>
+        <v>3150.954380280902</v>
       </c>
       <c r="D52">
-        <v>8907.177830623719</v>
+        <v>8861.531380280901</v>
       </c>
       <c r="E52">
-        <v>367.75</v>
+        <v>486.6769999999997</v>
       </c>
       <c r="F52">
-        <v>5946.35</v>
+        <v>6065.277</v>
       </c>
       <c r="G52">
         <v>354.7</v>
@@ -5557,28 +5557,28 @@
         <v>706.7</v>
       </c>
       <c r="M52">
-        <v>450.7333300000001</v>
+        <v>459.7479966</v>
       </c>
       <c r="N52">
-        <v>255.96667</v>
+        <v>246.9520034</v>
       </c>
       <c r="O52">
-        <v>25.596667</v>
+        <v>24.69520034</v>
       </c>
       <c r="P52">
-        <v>230.370003</v>
+        <v>222.25680306</v>
       </c>
       <c r="Q52">
-        <v>471.170003</v>
+        <v>463.05680306</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09946349480564404</v>
+        <v>0.1005010274656887</v>
       </c>
       <c r="T52">
-        <v>1.075612843074314</v>
+        <v>1.096408794927523</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.567889377073579</v>
+        <v>1.537146448111352</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08403770345818747</v>
+        <v>0.08423365951355291</v>
       </c>
       <c r="C53">
-        <v>3150.954380280902</v>
+        <v>2986.846391643464</v>
       </c>
       <c r="D53">
-        <v>8861.531380280901</v>
+        <v>8816.350391643464</v>
       </c>
       <c r="E53">
-        <v>486.6769999999997</v>
+        <v>605.6040000000003</v>
       </c>
       <c r="F53">
-        <v>6065.277</v>
+        <v>6184.204000000001</v>
       </c>
       <c r="G53">
         <v>354.7</v>
@@ -5639,28 +5639,28 @@
         <v>706.7</v>
       </c>
       <c r="M53">
-        <v>459.7479966</v>
+        <v>468.7626632000001</v>
       </c>
       <c r="N53">
-        <v>246.9520034</v>
+        <v>237.9373368</v>
       </c>
       <c r="O53">
-        <v>24.69520034</v>
+        <v>23.79373368</v>
       </c>
       <c r="P53">
-        <v>222.25680306</v>
+        <v>214.14360312</v>
       </c>
       <c r="Q53">
-        <v>463.05680306</v>
+        <v>454.94360312</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1005010274656887</v>
+        <v>0.1015817906532352</v>
       </c>
       <c r="T53">
-        <v>1.096408794927523</v>
+        <v>1.118071244774616</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.537146448111352</v>
+        <v>1.507585939493826</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08423365951355291</v>
+        <v>0.1052705173096292</v>
       </c>
       <c r="C54">
-        <v>2986.846391643464</v>
+        <v>-250.7403722149384</v>
       </c>
       <c r="D54">
-        <v>8816.350391643464</v>
+        <v>5697.690627785062</v>
       </c>
       <c r="E54">
-        <v>605.6040000000003</v>
+        <v>724.5309999999999</v>
       </c>
       <c r="F54">
-        <v>6184.204000000001</v>
+        <v>6303.131</v>
       </c>
       <c r="G54">
         <v>354.7</v>
@@ -5721,45 +5721,45 @@
         <v>706.7</v>
       </c>
       <c r="M54">
-        <v>468.7626632000001</v>
+        <v>747.5513366000001</v>
       </c>
       <c r="N54">
-        <v>237.9373368</v>
+        <v>-40.85133660000008</v>
       </c>
       <c r="O54">
-        <v>23.79373368</v>
+        <v>-4.085133660000008</v>
       </c>
       <c r="P54">
-        <v>214.14360312</v>
+        <v>-36.76620294000007</v>
       </c>
       <c r="Q54">
-        <v>454.94360312</v>
+        <v>204.0337970599999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1015817906532352</v>
+        <v>0.1028825915930598</v>
       </c>
       <c r="T54">
-        <v>1.118071244774616</v>
+        <v>1.144144056510523</v>
       </c>
       <c r="U54">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V54">
-        <v>0.1</v>
+        <v>0.09453531354972899</v>
       </c>
       <c r="W54">
-        <v>0.06822</v>
+        <v>0.1073881118130021</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.507585939493826</v>
+        <v>0.9453531354972898</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1052705173096292</v>
+        <v>0.1059985173096292</v>
       </c>
       <c r="C55">
-        <v>-250.7403722149384</v>
+        <v>-438.5713745459734</v>
       </c>
       <c r="D55">
-        <v>5697.690627785062</v>
+        <v>5628.786625454028</v>
       </c>
       <c r="E55">
-        <v>724.5309999999999</v>
+        <v>843.4580000000005</v>
       </c>
       <c r="F55">
-        <v>6303.131</v>
+        <v>6422.058000000001</v>
       </c>
       <c r="G55">
         <v>354.7</v>
@@ -5803,37 +5803,37 @@
         <v>706.7</v>
       </c>
       <c r="M55">
-        <v>747.5513366000001</v>
+        <v>761.6560788000002</v>
       </c>
       <c r="N55">
-        <v>-40.85133660000008</v>
+        <v>-54.95607880000011</v>
       </c>
       <c r="O55">
-        <v>-4.085133660000008</v>
+        <v>-5.495607880000012</v>
       </c>
       <c r="P55">
-        <v>-36.76620294000007</v>
+        <v>-49.46047092000011</v>
       </c>
       <c r="Q55">
-        <v>204.0337970599999</v>
+        <v>191.3395290799999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1028825915930598</v>
+        <v>0.1041235174972567</v>
       </c>
       <c r="T55">
-        <v>1.144144056510523</v>
+        <v>1.169016753391187</v>
       </c>
       <c r="U55">
         <v>0.1186</v>
       </c>
       <c r="V55">
-        <v>0.09453531354972899</v>
+        <v>0.09278465959510437</v>
       </c>
       <c r="W55">
-        <v>0.1073881118130021</v>
+        <v>0.1075957393720206</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.9453531354972898</v>
+        <v>0.9278465959510437</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1059985173096292</v>
+        <v>0.1067265173096292</v>
       </c>
       <c r="C56">
-        <v>-438.5713745459734</v>
+        <v>-624.7557338088664</v>
       </c>
       <c r="D56">
-        <v>5628.786625454028</v>
+        <v>5561.529266191134</v>
       </c>
       <c r="E56">
-        <v>843.4580000000005</v>
+        <v>962.3850000000002</v>
       </c>
       <c r="F56">
-        <v>6422.058000000001</v>
+        <v>6540.985000000001</v>
       </c>
       <c r="G56">
         <v>354.7</v>
@@ -5885,37 +5885,37 @@
         <v>706.7</v>
       </c>
       <c r="M56">
-        <v>761.6560788000002</v>
+        <v>775.7608210000002</v>
       </c>
       <c r="N56">
-        <v>-54.95607880000011</v>
+        <v>-69.06082100000015</v>
       </c>
       <c r="O56">
-        <v>-5.495607880000012</v>
+        <v>-6.906082100000015</v>
       </c>
       <c r="P56">
-        <v>-49.46047092000011</v>
+        <v>-62.15473890000013</v>
       </c>
       <c r="Q56">
-        <v>191.3395290799999</v>
+        <v>178.6452610999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1041235174972567</v>
+        <v>0.1054195956638624</v>
       </c>
       <c r="T56">
-        <v>1.169016753391187</v>
+        <v>1.194994903466547</v>
       </c>
       <c r="U56">
         <v>0.1186</v>
       </c>
       <c r="V56">
-        <v>0.09278465959510437</v>
+        <v>0.0910976657842843</v>
       </c>
       <c r="W56">
-        <v>0.1075957393720206</v>
+        <v>0.1077958168379839</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.9278465959510437</v>
+        <v>0.9109766578428429</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1067265173096292</v>
+        <v>0.1074545173096292</v>
       </c>
       <c r="C57">
-        <v>-624.7557338088664</v>
+        <v>-809.3517793624005</v>
       </c>
       <c r="D57">
-        <v>5561.529266191134</v>
+        <v>5495.860220637601</v>
       </c>
       <c r="E57">
-        <v>962.3850000000002</v>
+        <v>1081.312000000001</v>
       </c>
       <c r="F57">
-        <v>6540.985000000001</v>
+        <v>6659.912000000001</v>
       </c>
       <c r="G57">
         <v>354.7</v>
@@ -5967,37 +5967,37 @@
         <v>706.7</v>
       </c>
       <c r="M57">
-        <v>775.7608210000002</v>
+        <v>789.8655632000002</v>
       </c>
       <c r="N57">
-        <v>-69.06082100000015</v>
+        <v>-83.16556320000018</v>
       </c>
       <c r="O57">
-        <v>-6.906082100000015</v>
+        <v>-8.316556320000018</v>
       </c>
       <c r="P57">
-        <v>-62.15473890000013</v>
+        <v>-74.84900688000016</v>
       </c>
       <c r="Q57">
-        <v>178.6452610999999</v>
+        <v>165.9509931199999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1054195956638624</v>
+        <v>0.1067745864744047</v>
       </c>
       <c r="T57">
-        <v>1.194994903466547</v>
+        <v>1.222153878545332</v>
       </c>
       <c r="U57">
         <v>0.1186</v>
       </c>
       <c r="V57">
-        <v>0.0910976657842843</v>
+        <v>0.08947092175242206</v>
       </c>
       <c r="W57">
-        <v>0.1077958168379839</v>
+        <v>0.1079887486801628</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9109766578428429</v>
+        <v>0.8947092175242206</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1074545173096292</v>
+        <v>0.1081825173096292</v>
       </c>
       <c r="C58">
-        <v>-809.3517793624005</v>
+        <v>-992.415117765765</v>
       </c>
       <c r="D58">
-        <v>5495.860220637601</v>
+        <v>5431.723882234236</v>
       </c>
       <c r="E58">
-        <v>1081.312000000001</v>
+        <v>1200.239</v>
       </c>
       <c r="F58">
-        <v>6659.912000000001</v>
+        <v>6778.839000000001</v>
       </c>
       <c r="G58">
         <v>354.7</v>
@@ -6049,37 +6049,37 @@
         <v>706.7</v>
       </c>
       <c r="M58">
-        <v>789.8655632000002</v>
+        <v>803.9703054000001</v>
       </c>
       <c r="N58">
-        <v>-83.16556320000018</v>
+        <v>-97.2703054000001</v>
       </c>
       <c r="O58">
-        <v>-8.316556320000018</v>
+        <v>-9.72703054000001</v>
       </c>
       <c r="P58">
-        <v>-74.84900688000016</v>
+        <v>-87.54327486000008</v>
       </c>
       <c r="Q58">
-        <v>165.9509931199999</v>
+        <v>153.2567251399999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1067745864744047</v>
+        <v>0.1081926001133444</v>
       </c>
       <c r="T58">
-        <v>1.222153878545332</v>
+        <v>1.250576061767316</v>
       </c>
       <c r="U58">
         <v>0.1186</v>
       </c>
       <c r="V58">
-        <v>0.08947092175242206</v>
+        <v>0.08790125645851993</v>
       </c>
       <c r="W58">
-        <v>0.1079887486801628</v>
+        <v>0.1081749109840195</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8947092175242206</v>
+        <v>0.8790125645851993</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1081825173096292</v>
+        <v>0.1089105173096292</v>
       </c>
       <c r="C59">
-        <v>-992.415117765765</v>
+        <v>-1173.99878982038</v>
       </c>
       <c r="D59">
-        <v>5431.723882234236</v>
+        <v>5369.067210179622</v>
       </c>
       <c r="E59">
-        <v>1200.239</v>
+        <v>1319.166000000001</v>
       </c>
       <c r="F59">
-        <v>6778.839000000001</v>
+        <v>6897.766000000001</v>
       </c>
       <c r="G59">
         <v>354.7</v>
@@ -6131,37 +6131,37 @@
         <v>706.7</v>
       </c>
       <c r="M59">
-        <v>803.9703054000001</v>
+        <v>818.0750476000003</v>
       </c>
       <c r="N59">
-        <v>-97.2703054000001</v>
+        <v>-111.3750476000002</v>
       </c>
       <c r="O59">
-        <v>-9.72703054000001</v>
+        <v>-11.13750476000003</v>
       </c>
       <c r="P59">
-        <v>-87.54327486000008</v>
+        <v>-100.2375428400002</v>
       </c>
       <c r="Q59">
-        <v>153.2567251399999</v>
+        <v>140.5624571599998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1081926001133444</v>
+        <v>0.1096781382112812</v>
       </c>
       <c r="T59">
-        <v>1.250576061767316</v>
+        <v>1.280351682285586</v>
       </c>
       <c r="U59">
         <v>0.1186</v>
       </c>
       <c r="V59">
-        <v>0.08790125645851993</v>
+        <v>0.08638571755406269</v>
       </c>
       <c r="W59">
-        <v>0.1081749109840195</v>
+        <v>0.1083546538980882</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8790125645851993</v>
+        <v>0.8638571755406268</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1089105173096292</v>
+        <v>0.1096385173096292</v>
       </c>
       <c r="C60">
-        <v>-1173.998789820378</v>
+        <v>-1354.153416866492</v>
       </c>
       <c r="D60">
-        <v>5369.067210179622</v>
+        <v>5307.839583133508</v>
       </c>
       <c r="E60">
-        <v>1319.165999999999</v>
+        <v>1438.093</v>
       </c>
       <c r="F60">
-        <v>6897.766</v>
+        <v>7016.693</v>
       </c>
       <c r="G60">
         <v>354.7</v>
@@ -6213,37 +6213,37 @@
         <v>706.7</v>
       </c>
       <c r="M60">
-        <v>818.0750476000001</v>
+        <v>832.1797898000001</v>
       </c>
       <c r="N60">
-        <v>-111.3750476</v>
+        <v>-125.4797898</v>
       </c>
       <c r="O60">
-        <v>-11.13750476</v>
+        <v>-12.54797898000001</v>
       </c>
       <c r="P60">
-        <v>-100.23754284</v>
+        <v>-112.93181082</v>
       </c>
       <c r="Q60">
-        <v>140.56245716</v>
+        <v>127.86818918</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1096781382112811</v>
+        <v>0.111236141582288</v>
       </c>
       <c r="T60">
-        <v>1.280351682285585</v>
+        <v>1.311579772097429</v>
       </c>
       <c r="U60">
         <v>0.1186</v>
       </c>
       <c r="V60">
-        <v>0.08638571755406271</v>
+        <v>0.08492155284975655</v>
       </c>
       <c r="W60">
-        <v>0.1083546538980882</v>
+        <v>0.1085283038320189</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.863857175540627</v>
+        <v>0.8492155284975655</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1096385173096292</v>
+        <v>0.1103665173096292</v>
       </c>
       <c r="C61">
-        <v>-1354.153416866492</v>
+        <v>-1532.927337182648</v>
       </c>
       <c r="D61">
-        <v>5307.839583133508</v>
+        <v>5247.992662817353</v>
       </c>
       <c r="E61">
-        <v>1438.093</v>
+        <v>1557.02</v>
       </c>
       <c r="F61">
-        <v>7016.693</v>
+        <v>7135.62</v>
       </c>
       <c r="G61">
         <v>354.7</v>
@@ -6295,37 +6295,37 @@
         <v>706.7</v>
       </c>
       <c r="M61">
-        <v>832.1797898000001</v>
+        <v>846.284532</v>
       </c>
       <c r="N61">
-        <v>-125.4797898</v>
+        <v>-139.584532</v>
       </c>
       <c r="O61">
-        <v>-12.54797898000001</v>
+        <v>-13.9584532</v>
       </c>
       <c r="P61">
-        <v>-112.93181082</v>
+        <v>-125.6260788</v>
       </c>
       <c r="Q61">
-        <v>127.86818918</v>
+        <v>115.1739212</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.111236141582288</v>
+        <v>0.1128720451218452</v>
       </c>
       <c r="T61">
-        <v>1.311579772097429</v>
+        <v>1.344369266399865</v>
       </c>
       <c r="U61">
         <v>0.1186</v>
       </c>
       <c r="V61">
-        <v>0.08492155284975655</v>
+        <v>0.08350619363559396</v>
       </c>
       <c r="W61">
-        <v>0.1085283038320189</v>
+        <v>0.1086961654348186</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8492155284975655</v>
+        <v>0.8350619363559395</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1103665173096292</v>
+        <v>0.1110945173096292</v>
       </c>
       <c r="C62">
-        <v>-1532.927337182648</v>
+        <v>-1710.366733260468</v>
       </c>
       <c r="D62">
-        <v>5247.992662817353</v>
+        <v>5189.480266739532</v>
       </c>
       <c r="E62">
-        <v>1557.02</v>
+        <v>1675.947</v>
       </c>
       <c r="F62">
-        <v>7135.62</v>
+        <v>7254.547</v>
       </c>
       <c r="G62">
         <v>354.7</v>
@@ -6377,37 +6377,37 @@
         <v>706.7</v>
       </c>
       <c r="M62">
-        <v>846.284532</v>
+        <v>860.3892742000002</v>
       </c>
       <c r="N62">
-        <v>-139.584532</v>
+        <v>-153.6892742000001</v>
       </c>
       <c r="O62">
-        <v>-13.9584532</v>
+        <v>-15.36892742000001</v>
       </c>
       <c r="P62">
-        <v>-125.6260788</v>
+        <v>-138.3203467800001</v>
       </c>
       <c r="Q62">
-        <v>115.1739212</v>
+        <v>102.4796532199999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1128720451218452</v>
+        <v>0.1145918411506105</v>
       </c>
       <c r="T62">
-        <v>1.344369266399865</v>
+        <v>1.378840273230631</v>
       </c>
       <c r="U62">
         <v>0.1186</v>
       </c>
       <c r="V62">
-        <v>0.08350619363559396</v>
+        <v>0.08213723964156781</v>
       </c>
       <c r="W62">
-        <v>0.1086961654348186</v>
+        <v>0.1088585233785101</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8350619363559395</v>
+        <v>0.8213723964156781</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1110945173096292</v>
+        <v>0.1118225173096292</v>
       </c>
       <c r="C63">
-        <v>-1710.366733260468</v>
+        <v>-1886.515750658999</v>
       </c>
       <c r="D63">
-        <v>5189.480266739532</v>
+        <v>5132.258249341002</v>
       </c>
       <c r="E63">
-        <v>1675.947</v>
+        <v>1794.874</v>
       </c>
       <c r="F63">
-        <v>7254.547</v>
+        <v>7373.474</v>
       </c>
       <c r="G63">
         <v>354.7</v>
@@ -6459,37 +6459,37 @@
         <v>706.7</v>
       </c>
       <c r="M63">
-        <v>860.3892742000002</v>
+        <v>874.4940164000001</v>
       </c>
       <c r="N63">
-        <v>-153.6892742000001</v>
+        <v>-167.7940164</v>
       </c>
       <c r="O63">
-        <v>-15.36892742000001</v>
+        <v>-16.77940164</v>
       </c>
       <c r="P63">
-        <v>-138.3203467800001</v>
+        <v>-151.01461476</v>
       </c>
       <c r="Q63">
-        <v>102.4796532199999</v>
+        <v>89.78538523999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1145918411506105</v>
+        <v>0.1164021527598371</v>
       </c>
       <c r="T63">
-        <v>1.378840273230631</v>
+        <v>1.415125543578805</v>
       </c>
       <c r="U63">
         <v>0.1186</v>
       </c>
       <c r="V63">
-        <v>0.08213723964156781</v>
+        <v>0.08081244545380059</v>
       </c>
       <c r="W63">
-        <v>0.1088585233785101</v>
+        <v>0.1090156439691793</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8213723964156781</v>
+        <v>0.808124454538006</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1118225173096292</v>
+        <v>0.1649158171370879</v>
       </c>
       <c r="C64">
-        <v>-1886.515750658999</v>
+        <v>-4293.035889617267</v>
       </c>
       <c r="D64">
-        <v>5132.258249341002</v>
+        <v>2844.665110382734</v>
       </c>
       <c r="E64">
-        <v>1794.874</v>
+        <v>1913.801</v>
       </c>
       <c r="F64">
-        <v>7373.474</v>
+        <v>7492.401000000001</v>
       </c>
       <c r="G64">
         <v>354.7</v>
@@ -6541,45 +6541,45 @@
         <v>706.7</v>
       </c>
       <c r="M64">
-        <v>874.4940164000001</v>
+        <v>1504.4741208</v>
       </c>
       <c r="N64">
-        <v>-167.7940164</v>
+        <v>-797.7741208000002</v>
       </c>
       <c r="O64">
-        <v>-16.77940164</v>
+        <v>-79.77741208000003</v>
       </c>
       <c r="P64">
-        <v>-151.01461476</v>
+        <v>-717.9967087200002</v>
       </c>
       <c r="Q64">
-        <v>89.78538523999998</v>
+        <v>-477.1967087200002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1164021527598371</v>
+        <v>0.1198759942599912</v>
       </c>
       <c r="T64">
-        <v>1.415125543578805</v>
+        <v>1.484754041422694</v>
       </c>
       <c r="U64">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.08081244545380059</v>
+        <v>0.04697322408073155</v>
       </c>
       <c r="W64">
-        <v>0.1090156439691793</v>
+        <v>0.1913677766045891</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.808124454538006</v>
+        <v>0.4697322408073156</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1649158171370879</v>
+        <v>0.1664658171370879</v>
       </c>
       <c r="C65">
-        <v>-4293.035889617267</v>
+        <v>-4448.503734619659</v>
       </c>
       <c r="D65">
-        <v>2844.665110382734</v>
+        <v>2808.124265380342</v>
       </c>
       <c r="E65">
-        <v>1913.801</v>
+        <v>2032.728</v>
       </c>
       <c r="F65">
-        <v>7492.401000000001</v>
+        <v>7611.328</v>
       </c>
       <c r="G65">
         <v>354.7</v>
@@ -6623,37 +6623,37 @@
         <v>706.7</v>
       </c>
       <c r="M65">
-        <v>1504.4741208</v>
+        <v>1528.3546624</v>
       </c>
       <c r="N65">
-        <v>-797.7741208000002</v>
+        <v>-821.6546624</v>
       </c>
       <c r="O65">
-        <v>-79.77741208000003</v>
+        <v>-82.16546624</v>
       </c>
       <c r="P65">
-        <v>-717.9967087200002</v>
+        <v>-739.48919616</v>
       </c>
       <c r="Q65">
-        <v>-477.1967087200002</v>
+        <v>-498.68919616</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1198759942599912</v>
+        <v>0.1219336607672132</v>
       </c>
       <c r="T65">
-        <v>1.484754041422694</v>
+        <v>1.525997209239991</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.04697322408073155</v>
+        <v>0.04623926745447013</v>
       </c>
       <c r="W65">
-        <v>0.1913677766045891</v>
+        <v>0.1915151550951424</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4697322408073156</v>
+        <v>0.4623926745447013</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1664658171370879</v>
+        <v>0.1680158171370879</v>
       </c>
       <c r="C66">
-        <v>-4448.503734619659</v>
+        <v>-4603.04472234481</v>
       </c>
       <c r="D66">
-        <v>2808.124265380342</v>
+        <v>2772.510277655191</v>
       </c>
       <c r="E66">
-        <v>2032.728</v>
+        <v>2151.655000000001</v>
       </c>
       <c r="F66">
-        <v>7611.328</v>
+        <v>7730.255000000001</v>
       </c>
       <c r="G66">
         <v>354.7</v>
@@ -6705,37 +6705,37 @@
         <v>706.7</v>
       </c>
       <c r="M66">
-        <v>1528.3546624</v>
+        <v>1552.235204</v>
       </c>
       <c r="N66">
-        <v>-821.6546624</v>
+        <v>-845.5352040000002</v>
       </c>
       <c r="O66">
-        <v>-82.16546624</v>
+        <v>-84.55352040000002</v>
       </c>
       <c r="P66">
-        <v>-739.48919616</v>
+        <v>-760.9816836000002</v>
       </c>
       <c r="Q66">
-        <v>-498.68919616</v>
+        <v>-520.1816836000003</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1219336607672132</v>
+        <v>0.124108908217705</v>
       </c>
       <c r="T66">
-        <v>1.525997209239991</v>
+        <v>1.569597129503991</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.04623926745447013</v>
+        <v>0.04552789410901674</v>
       </c>
       <c r="W66">
-        <v>0.1915151550951424</v>
+        <v>0.1916579988629095</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4623926745447013</v>
+        <v>0.4552789410901673</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1680158171370879</v>
+        <v>0.1695658171370879</v>
       </c>
       <c r="C67">
-        <v>-4603.04472234481</v>
+        <v>-4756.693675706177</v>
       </c>
       <c r="D67">
-        <v>2772.510277655191</v>
+        <v>2737.788324293824</v>
       </c>
       <c r="E67">
-        <v>2151.655000000001</v>
+        <v>2270.582</v>
       </c>
       <c r="F67">
-        <v>7730.255000000001</v>
+        <v>7849.182000000001</v>
       </c>
       <c r="G67">
         <v>354.7</v>
@@ -6787,37 +6787,37 @@
         <v>706.7</v>
       </c>
       <c r="M67">
-        <v>1552.235204</v>
+        <v>1576.1157456</v>
       </c>
       <c r="N67">
-        <v>-845.5352040000002</v>
+        <v>-869.4157456</v>
       </c>
       <c r="O67">
-        <v>-84.55352040000002</v>
+        <v>-86.94157456000001</v>
       </c>
       <c r="P67">
-        <v>-760.9816836000002</v>
+        <v>-782.47417104</v>
       </c>
       <c r="Q67">
-        <v>-520.1816836000003</v>
+        <v>-541.6741710399999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.124108908217705</v>
+        <v>0.1264121114005786</v>
       </c>
       <c r="T67">
-        <v>1.569597129503991</v>
+        <v>1.61576175095999</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.04552789410901674</v>
+        <v>0.0448380775316074</v>
       </c>
       <c r="W67">
-        <v>0.1916579988629095</v>
+        <v>0.1917965140316532</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4552789410901673</v>
+        <v>0.448380775316074</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1695658171370879</v>
+        <v>0.1711158171370879</v>
       </c>
       <c r="C68">
-        <v>-4756.693675706177</v>
+        <v>-4909.483694753591</v>
       </c>
       <c r="D68">
-        <v>2737.788324293824</v>
+        <v>2703.925305246411</v>
       </c>
       <c r="E68">
-        <v>2270.582</v>
+        <v>2389.509000000001</v>
       </c>
       <c r="F68">
-        <v>7849.182000000001</v>
+        <v>7968.109000000001</v>
       </c>
       <c r="G68">
         <v>354.7</v>
@@ -6869,37 +6869,37 @@
         <v>706.7</v>
       </c>
       <c r="M68">
-        <v>1576.1157456</v>
+        <v>1599.9962872</v>
       </c>
       <c r="N68">
-        <v>-869.4157456</v>
+        <v>-893.2962872000003</v>
       </c>
       <c r="O68">
-        <v>-86.94157456000001</v>
+        <v>-89.32962872000003</v>
       </c>
       <c r="P68">
-        <v>-782.47417104</v>
+        <v>-803.9666584800002</v>
       </c>
       <c r="Q68">
-        <v>-541.6741710399999</v>
+        <v>-563.1666584800003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1264121114005786</v>
+        <v>0.1288549026551416</v>
       </c>
       <c r="T68">
-        <v>1.61576175095999</v>
+        <v>1.664724228261808</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.0448380775316074</v>
+        <v>0.04416885249382221</v>
       </c>
       <c r="W68">
-        <v>0.1917965140316532</v>
+        <v>0.1919308944192405</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.448380775316074</v>
+        <v>0.4416885249382221</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1711158171370879</v>
+        <v>0.1726658171370879</v>
       </c>
       <c r="C69">
-        <v>-4909.483694753591</v>
+        <v>-5061.446261919829</v>
       </c>
       <c r="D69">
-        <v>2703.925305246411</v>
+        <v>2670.889738080172</v>
       </c>
       <c r="E69">
-        <v>2389.509000000001</v>
+        <v>2508.436000000001</v>
       </c>
       <c r="F69">
-        <v>7968.109000000001</v>
+        <v>8087.036000000001</v>
       </c>
       <c r="G69">
         <v>354.7</v>
@@ -6951,37 +6951,37 @@
         <v>706.7</v>
       </c>
       <c r="M69">
-        <v>1599.9962872</v>
+        <v>1623.8768288</v>
       </c>
       <c r="N69">
-        <v>-893.2962872000003</v>
+        <v>-917.1768288000003</v>
       </c>
       <c r="O69">
-        <v>-89.32962872000003</v>
+        <v>-91.71768288000004</v>
       </c>
       <c r="P69">
-        <v>-803.9666584800002</v>
+        <v>-825.4591459200003</v>
       </c>
       <c r="Q69">
-        <v>-563.1666584800003</v>
+        <v>-584.6591459200004</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1288549026551416</v>
+        <v>0.1314503683631148</v>
       </c>
       <c r="T69">
-        <v>1.664724228261808</v>
+        <v>1.71674686039499</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.04416885249382221</v>
+        <v>0.04351931054538365</v>
       </c>
       <c r="W69">
-        <v>0.1919308944192405</v>
+        <v>0.192061322442487</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4416885249382221</v>
+        <v>0.4351931054538364</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1726658171370879</v>
+        <v>0.1742158171370879</v>
       </c>
       <c r="C70">
-        <v>-5061.446261919829</v>
+        <v>-5212.611339645136</v>
       </c>
       <c r="D70">
-        <v>2670.889738080172</v>
+        <v>2638.651660354865</v>
       </c>
       <c r="E70">
-        <v>2508.436000000001</v>
+        <v>2627.363000000001</v>
       </c>
       <c r="F70">
-        <v>8087.036000000001</v>
+        <v>8205.963000000002</v>
       </c>
       <c r="G70">
         <v>354.7</v>
@@ -7033,37 +7033,37 @@
         <v>706.7</v>
       </c>
       <c r="M70">
-        <v>1623.8768288</v>
+        <v>1647.7573704</v>
       </c>
       <c r="N70">
-        <v>-917.1768288000003</v>
+        <v>-941.0573704000003</v>
       </c>
       <c r="O70">
-        <v>-91.71768288000004</v>
+        <v>-94.10573704000004</v>
       </c>
       <c r="P70">
-        <v>-825.4591459200003</v>
+        <v>-846.9516333600003</v>
       </c>
       <c r="Q70">
-        <v>-584.6591459200004</v>
+        <v>-606.1516333600002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1314503683631148</v>
+        <v>0.1342132834716024</v>
       </c>
       <c r="T70">
-        <v>1.71674686039499</v>
+        <v>1.772125791375474</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.04351931054538365</v>
+        <v>0.04288859589979838</v>
       </c>
       <c r="W70">
-        <v>0.192061322442487</v>
+        <v>0.1921879699433205</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4351931054538364</v>
+        <v>0.4288859589979838</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1742158171370879</v>
+        <v>0.1757658171370879</v>
       </c>
       <c r="C71">
-        <v>-5212.611339645136</v>
+        <v>-5363.007461015996</v>
       </c>
       <c r="D71">
-        <v>2638.651660354865</v>
+        <v>2607.182538984005</v>
       </c>
       <c r="E71">
-        <v>2627.363000000001</v>
+        <v>2746.290000000001</v>
       </c>
       <c r="F71">
-        <v>8205.963000000002</v>
+        <v>8324.890000000001</v>
       </c>
       <c r="G71">
         <v>354.7</v>
@@ -7115,37 +7115,37 @@
         <v>706.7</v>
       </c>
       <c r="M71">
-        <v>1647.7573704</v>
+        <v>1671.637912</v>
       </c>
       <c r="N71">
-        <v>-941.0573704000003</v>
+        <v>-964.9379120000003</v>
       </c>
       <c r="O71">
-        <v>-94.10573704000004</v>
+        <v>-96.49379120000003</v>
       </c>
       <c r="P71">
-        <v>-846.9516333600003</v>
+        <v>-868.4441208000003</v>
       </c>
       <c r="Q71">
-        <v>-606.1516333600002</v>
+        <v>-627.6441208000003</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1342132834716024</v>
+        <v>0.1371603929206558</v>
       </c>
       <c r="T71">
-        <v>1.772125791375474</v>
+        <v>1.831196651087989</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.04288859589979838</v>
+        <v>0.0422759016726584</v>
       </c>
       <c r="W71">
-        <v>0.1921879699433205</v>
+        <v>0.1923109989441302</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4288859589979838</v>
+        <v>0.422759016726584</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1757658171370879</v>
+        <v>0.1773158171370879</v>
       </c>
       <c r="C72">
-        <v>-5363.007461015996</v>
+        <v>-5512.661813994482</v>
       </c>
       <c r="D72">
-        <v>2607.182538984005</v>
+        <v>2576.455186005519</v>
       </c>
       <c r="E72">
-        <v>2746.290000000001</v>
+        <v>2865.217000000001</v>
       </c>
       <c r="F72">
-        <v>8324.890000000001</v>
+        <v>8443.817000000001</v>
       </c>
       <c r="G72">
         <v>354.7</v>
@@ -7197,37 +7197,37 @@
         <v>706.7</v>
       </c>
       <c r="M72">
-        <v>1671.637912</v>
+        <v>1695.5184536</v>
       </c>
       <c r="N72">
-        <v>-964.9379120000003</v>
+        <v>-988.8184536000001</v>
       </c>
       <c r="O72">
-        <v>-96.49379120000003</v>
+        <v>-98.88184536000001</v>
       </c>
       <c r="P72">
-        <v>-868.4441208000003</v>
+        <v>-889.9366082400001</v>
       </c>
       <c r="Q72">
-        <v>-627.6441208000003</v>
+        <v>-649.13660824</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1371603929206558</v>
+        <v>0.1403107512972302</v>
       </c>
       <c r="T72">
-        <v>1.831196651087989</v>
+        <v>1.894341363194472</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.0422759016726584</v>
+        <v>0.04168046643783223</v>
       </c>
       <c r="W72">
-        <v>0.1923109989441302</v>
+        <v>0.1924305623392833</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.422759016726584</v>
+        <v>0.4168046643783223</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1773158171370879</v>
+        <v>0.1788658171370879</v>
       </c>
       <c r="C73">
-        <v>-5512.661813994482</v>
+        <v>-5661.600319760792</v>
       </c>
       <c r="D73">
-        <v>2576.455186005519</v>
+        <v>2546.443680239209</v>
       </c>
       <c r="E73">
-        <v>2865.217000000001</v>
+        <v>2984.144</v>
       </c>
       <c r="F73">
-        <v>8443.817000000001</v>
+        <v>8562.744000000001</v>
       </c>
       <c r="G73">
         <v>354.7</v>
@@ -7279,37 +7279,37 @@
         <v>706.7</v>
       </c>
       <c r="M73">
-        <v>1695.5184536</v>
+        <v>1719.3989952</v>
       </c>
       <c r="N73">
-        <v>-988.8184536000001</v>
+        <v>-1012.6989952</v>
       </c>
       <c r="O73">
-        <v>-98.88184536000001</v>
+        <v>-101.26989952</v>
       </c>
       <c r="P73">
-        <v>-889.9366082400001</v>
+        <v>-911.42909568</v>
       </c>
       <c r="Q73">
-        <v>-649.13660824</v>
+        <v>-670.6290956800001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1403107512972301</v>
+        <v>0.1436861352721312</v>
       </c>
       <c r="T73">
-        <v>1.894341363194471</v>
+        <v>1.961996411879988</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.04168046643783223</v>
+        <v>0.04110157107064012</v>
       </c>
       <c r="W73">
-        <v>0.1924305623392833</v>
+        <v>0.1925468045290155</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4168046643783223</v>
+        <v>0.4110157107064011</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1788658171370879</v>
+        <v>0.1804158171370879</v>
       </c>
       <c r="C74">
-        <v>-5661.600319760792</v>
+        <v>-5809.847705643464</v>
       </c>
       <c r="D74">
-        <v>2546.443680239209</v>
+        <v>2517.123294356536</v>
       </c>
       <c r="E74">
-        <v>2984.144</v>
+        <v>3103.071</v>
       </c>
       <c r="F74">
-        <v>8562.744000000001</v>
+        <v>8681.671</v>
       </c>
       <c r="G74">
         <v>354.7</v>
@@ -7361,37 +7361,37 @@
         <v>706.7</v>
       </c>
       <c r="M74">
-        <v>1719.3989952</v>
+        <v>1743.2795368</v>
       </c>
       <c r="N74">
-        <v>-1012.6989952</v>
+        <v>-1036.5795368</v>
       </c>
       <c r="O74">
-        <v>-101.26989952</v>
+        <v>-103.65795368</v>
       </c>
       <c r="P74">
-        <v>-911.42909568</v>
+        <v>-932.9215831200002</v>
       </c>
       <c r="Q74">
-        <v>-670.6290956800001</v>
+        <v>-692.1215831200002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1436861352721312</v>
+        <v>0.1473115476896175</v>
       </c>
       <c r="T74">
-        <v>1.961996411879988</v>
+        <v>2.034662945653321</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.04110157107064012</v>
+        <v>0.04053853585049436</v>
       </c>
       <c r="W74">
-        <v>0.1925468045290155</v>
+        <v>0.1926598620012207</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4110157107064011</v>
+        <v>0.4053853585049436</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1804158171370879</v>
+        <v>0.1819658171370879</v>
       </c>
       <c r="C75">
-        <v>-5809.847705643464</v>
+        <v>-5957.427573068514</v>
       </c>
       <c r="D75">
-        <v>2517.123294356536</v>
+        <v>2488.470426931486</v>
       </c>
       <c r="E75">
-        <v>3103.071</v>
+        <v>3221.998</v>
       </c>
       <c r="F75">
-        <v>8681.671</v>
+        <v>8800.598</v>
       </c>
       <c r="G75">
         <v>354.7</v>
@@ -7443,37 +7443,37 @@
         <v>706.7</v>
       </c>
       <c r="M75">
-        <v>1743.2795368</v>
+        <v>1767.1600784</v>
       </c>
       <c r="N75">
-        <v>-1036.5795368</v>
+        <v>-1060.4600784</v>
       </c>
       <c r="O75">
-        <v>-103.65795368</v>
+        <v>-106.04600784</v>
       </c>
       <c r="P75">
-        <v>-932.9215831200002</v>
+        <v>-954.4140705599999</v>
       </c>
       <c r="Q75">
-        <v>-692.1215831200002</v>
+        <v>-713.6140705599998</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1473115476896175</v>
+        <v>0.1512158379853721</v>
       </c>
       <c r="T75">
-        <v>2.034662945653321</v>
+        <v>2.112919212793833</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.04053853585049436</v>
+        <v>0.03999071779846066</v>
       </c>
       <c r="W75">
-        <v>0.1926598620012207</v>
+        <v>0.1927698638660691</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4053853585049436</v>
+        <v>0.3999071779846065</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1819658171370879</v>
+        <v>0.1835158171370879</v>
       </c>
       <c r="C76">
-        <v>-5957.427573068514</v>
+        <v>-6104.362460919949</v>
       </c>
       <c r="D76">
-        <v>2488.470426931486</v>
+        <v>2460.462539080053</v>
       </c>
       <c r="E76">
-        <v>3221.998</v>
+        <v>3340.925000000001</v>
       </c>
       <c r="F76">
-        <v>8800.598</v>
+        <v>8919.525000000001</v>
       </c>
       <c r="G76">
         <v>354.7</v>
@@ -7525,37 +7525,37 @@
         <v>706.7</v>
       </c>
       <c r="M76">
-        <v>1767.1600784</v>
+        <v>1791.04062</v>
       </c>
       <c r="N76">
-        <v>-1060.4600784</v>
+        <v>-1084.34062</v>
       </c>
       <c r="O76">
-        <v>-106.04600784</v>
+        <v>-108.434062</v>
       </c>
       <c r="P76">
-        <v>-954.4140705599999</v>
+        <v>-975.9065580000004</v>
       </c>
       <c r="Q76">
-        <v>-713.6140705599998</v>
+        <v>-735.1065580000004</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1512158379853721</v>
+        <v>0.155432471504787</v>
       </c>
       <c r="T76">
-        <v>2.112919212793833</v>
+        <v>2.197435981305587</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.03999071779846066</v>
+        <v>0.03945750822781451</v>
       </c>
       <c r="W76">
-        <v>0.1927698638660691</v>
+        <v>0.1928769323478549</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3999071779846065</v>
+        <v>0.394575082278145</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1835158171370879</v>
+        <v>0.1850658171370879</v>
       </c>
       <c r="C77">
-        <v>-6104.362460919949</v>
+        <v>-6250.673904669126</v>
       </c>
       <c r="D77">
-        <v>2460.462539080053</v>
+        <v>2433.078095330875</v>
       </c>
       <c r="E77">
-        <v>3340.925000000001</v>
+        <v>3459.852000000001</v>
       </c>
       <c r="F77">
-        <v>8919.525000000001</v>
+        <v>9038.452000000001</v>
       </c>
       <c r="G77">
         <v>354.7</v>
@@ -7607,37 +7607,37 @@
         <v>706.7</v>
       </c>
       <c r="M77">
-        <v>1791.04062</v>
+        <v>1814.9211616</v>
       </c>
       <c r="N77">
-        <v>-1084.34062</v>
+        <v>-1108.2211616</v>
       </c>
       <c r="O77">
-        <v>-108.434062</v>
+        <v>-110.82211616</v>
       </c>
       <c r="P77">
-        <v>-975.9065580000004</v>
+        <v>-997.3990454400001</v>
       </c>
       <c r="Q77">
-        <v>-735.1065580000004</v>
+        <v>-756.5990454400001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.155432471504787</v>
+        <v>0.1600004911508197</v>
       </c>
       <c r="T77">
-        <v>2.197435981305587</v>
+        <v>2.288995813859986</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.03945750822781451</v>
+        <v>0.03893833048797485</v>
       </c>
       <c r="W77">
-        <v>0.1928769323478549</v>
+        <v>0.1929811832380146</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.394575082278145</v>
+        <v>0.3893833048797484</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1850658171370879</v>
+        <v>0.1866158171370879</v>
       </c>
       <c r="C78">
-        <v>-6250.673904669126</v>
+        <v>-6396.382491599034</v>
       </c>
       <c r="D78">
-        <v>2433.078095330875</v>
+        <v>2406.296508400967</v>
       </c>
       <c r="E78">
-        <v>3459.852000000001</v>
+        <v>3578.779</v>
       </c>
       <c r="F78">
-        <v>9038.452000000001</v>
+        <v>9157.379000000001</v>
       </c>
       <c r="G78">
         <v>354.7</v>
@@ -7689,37 +7689,37 @@
         <v>706.7</v>
       </c>
       <c r="M78">
-        <v>1814.9211616</v>
+        <v>1838.8017032</v>
       </c>
       <c r="N78">
-        <v>-1108.2211616</v>
+        <v>-1132.1017032</v>
       </c>
       <c r="O78">
-        <v>-110.82211616</v>
+        <v>-113.21017032</v>
       </c>
       <c r="P78">
-        <v>-997.3990454400001</v>
+        <v>-1018.89153288</v>
       </c>
       <c r="Q78">
-        <v>-756.5990454400001</v>
+        <v>-778.0915328800002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1600004911508197</v>
+        <v>0.1649657298965076</v>
       </c>
       <c r="T78">
-        <v>2.288995813859986</v>
+        <v>2.388517370984333</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.03893833048797485</v>
+        <v>0.03843263788423491</v>
       </c>
       <c r="W78">
-        <v>0.1929811832380146</v>
+        <v>0.1930827263128456</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3893833048797484</v>
+        <v>0.3843263788423491</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1866158171370879</v>
+        <v>0.1881658171370879</v>
       </c>
       <c r="C79">
-        <v>-6396.382491599034</v>
+        <v>-6541.507912421006</v>
       </c>
       <c r="D79">
-        <v>2406.296508400967</v>
+        <v>2380.098087578994</v>
       </c>
       <c r="E79">
-        <v>3578.779</v>
+        <v>3697.706</v>
       </c>
       <c r="F79">
-        <v>9157.379000000001</v>
+        <v>9276.306</v>
       </c>
       <c r="G79">
         <v>354.7</v>
@@ -7771,37 +7771,37 @@
         <v>706.7</v>
       </c>
       <c r="M79">
-        <v>1838.8017032</v>
+        <v>1862.6822448</v>
       </c>
       <c r="N79">
-        <v>-1132.1017032</v>
+        <v>-1155.9822448</v>
       </c>
       <c r="O79">
-        <v>-113.21017032</v>
+        <v>-115.59822448</v>
       </c>
       <c r="P79">
-        <v>-1018.89153288</v>
+        <v>-1040.38402032</v>
       </c>
       <c r="Q79">
-        <v>-778.0915328800002</v>
+        <v>-799.5840203200003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1649657298965076</v>
+        <v>0.1703823539827125</v>
       </c>
       <c r="T79">
-        <v>2.388517370984333</v>
+        <v>2.497086342392713</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.03843263788423491</v>
+        <v>0.03793991175751395</v>
       </c>
       <c r="W79">
-        <v>0.1930827263128456</v>
+        <v>0.1931816657190912</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3843263788423491</v>
+        <v>0.3793991175751394</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1881658171370879</v>
+        <v>0.1897158171370879</v>
       </c>
       <c r="C80">
-        <v>-6541.507912421006</v>
+        <v>-6686.069009555955</v>
       </c>
       <c r="D80">
-        <v>2380.098087578994</v>
+        <v>2354.463990444046</v>
       </c>
       <c r="E80">
-        <v>3697.706</v>
+        <v>3816.633</v>
       </c>
       <c r="F80">
-        <v>9276.306</v>
+        <v>9395.233</v>
       </c>
       <c r="G80">
         <v>354.7</v>
@@ -7853,37 +7853,37 @@
         <v>706.7</v>
       </c>
       <c r="M80">
-        <v>1862.6822448</v>
+        <v>1886.5627864</v>
       </c>
       <c r="N80">
-        <v>-1155.9822448</v>
+        <v>-1179.8627864</v>
       </c>
       <c r="O80">
-        <v>-115.59822448</v>
+        <v>-117.98627864</v>
       </c>
       <c r="P80">
-        <v>-1040.38402032</v>
+        <v>-1061.87650776</v>
       </c>
       <c r="Q80">
-        <v>-799.5840203200003</v>
+        <v>-821.0765077600001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1703823539827125</v>
+        <v>0.1763148470295083</v>
       </c>
       <c r="T80">
-        <v>2.497086342392713</v>
+        <v>2.615995215839985</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.03793991175751395</v>
+        <v>0.03745965970995049</v>
       </c>
       <c r="W80">
-        <v>0.1931816657190912</v>
+        <v>0.193278100330242</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3793991175751394</v>
+        <v>0.3745965970995049</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1897158171370879</v>
+        <v>0.1912658171370879</v>
       </c>
       <c r="C81">
-        <v>-6686.069009555955</v>
+        <v>-6830.083822328828</v>
       </c>
       <c r="D81">
-        <v>2354.463990444046</v>
+        <v>2329.376177671173</v>
       </c>
       <c r="E81">
-        <v>3816.633</v>
+        <v>3935.560000000001</v>
       </c>
       <c r="F81">
-        <v>9395.233</v>
+        <v>9514.160000000002</v>
       </c>
       <c r="G81">
         <v>354.7</v>
@@ -7935,37 +7935,37 @@
         <v>706.7</v>
       </c>
       <c r="M81">
-        <v>1886.5627864</v>
+        <v>1910.443328</v>
       </c>
       <c r="N81">
-        <v>-1179.8627864</v>
+        <v>-1203.743328</v>
       </c>
       <c r="O81">
-        <v>-117.98627864</v>
+        <v>-120.3743328</v>
       </c>
       <c r="P81">
-        <v>-1061.87650776</v>
+        <v>-1083.3689952</v>
       </c>
       <c r="Q81">
-        <v>-821.0765077600001</v>
+        <v>-842.5689952000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1763148470295083</v>
+        <v>0.1828405893809837</v>
       </c>
       <c r="T81">
-        <v>2.615995215839985</v>
+        <v>2.746794976631984</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.03745965970995049</v>
+        <v>0.0369914139635761</v>
       </c>
       <c r="W81">
-        <v>0.193278100330242</v>
+        <v>0.1933721240761139</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3745965970995049</v>
+        <v>0.369914139635761</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1912658171370879</v>
+        <v>0.1928158171370879</v>
       </c>
       <c r="C82">
-        <v>-6830.083822328828</v>
+        <v>-6973.569629304159</v>
       </c>
       <c r="D82">
-        <v>2329.376177671173</v>
+        <v>2304.817370695842</v>
       </c>
       <c r="E82">
-        <v>3935.560000000001</v>
+        <v>4054.487000000001</v>
       </c>
       <c r="F82">
-        <v>9514.160000000002</v>
+        <v>9633.087000000001</v>
       </c>
       <c r="G82">
         <v>354.7</v>
@@ -8017,37 +8017,37 @@
         <v>706.7</v>
       </c>
       <c r="M82">
-        <v>1910.443328</v>
+        <v>1934.3238696</v>
       </c>
       <c r="N82">
-        <v>-1203.743328</v>
+        <v>-1227.6238696</v>
       </c>
       <c r="O82">
-        <v>-120.3743328</v>
+        <v>-122.76238696</v>
       </c>
       <c r="P82">
-        <v>-1083.3689952</v>
+        <v>-1104.86148264</v>
       </c>
       <c r="Q82">
-        <v>-842.5689952000002</v>
+        <v>-864.0614826400003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1828405893809837</v>
+        <v>0.1900532519799829</v>
       </c>
       <c r="T82">
-        <v>2.746794976631984</v>
+        <v>2.891363133296825</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.0369914139635761</v>
+        <v>0.03653472984056898</v>
       </c>
       <c r="W82">
-        <v>0.1933721240761139</v>
+        <v>0.1934638262480138</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.369914139635761</v>
+        <v>0.3653472984056899</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1928158171370879</v>
+        <v>0.1943658171370879</v>
       </c>
       <c r="C83">
-        <v>-6973.569629304159</v>
+        <v>-7116.542987971457</v>
       </c>
       <c r="D83">
-        <v>2304.817370695842</v>
+        <v>2280.771012028545</v>
       </c>
       <c r="E83">
-        <v>4054.487000000001</v>
+        <v>4173.414000000001</v>
       </c>
       <c r="F83">
-        <v>9633.087000000001</v>
+        <v>9752.014000000001</v>
       </c>
       <c r="G83">
         <v>354.7</v>
@@ -8099,37 +8099,37 @@
         <v>706.7</v>
       </c>
       <c r="M83">
-        <v>1934.3238696</v>
+        <v>1958.2044112</v>
       </c>
       <c r="N83">
-        <v>-1227.6238696</v>
+        <v>-1251.5044112</v>
       </c>
       <c r="O83">
-        <v>-122.76238696</v>
+        <v>-125.15044112</v>
       </c>
       <c r="P83">
-        <v>-1104.86148264</v>
+        <v>-1126.35397008</v>
       </c>
       <c r="Q83">
-        <v>-864.0614826400003</v>
+        <v>-885.5539700800002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1900532519799829</v>
+        <v>0.1980673215344264</v>
       </c>
       <c r="T83">
-        <v>2.891363133296825</v>
+        <v>3.051994418479982</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.03653472984056898</v>
+        <v>0.03608918435470839</v>
       </c>
       <c r="W83">
-        <v>0.1934638262480138</v>
+        <v>0.1935532917815745</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3653472984056899</v>
+        <v>0.3608918435470839</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1943658171370879</v>
+        <v>0.1959158171370879</v>
       </c>
       <c r="C84">
-        <v>-7116.542987971457</v>
+        <v>-7259.019771972005</v>
       </c>
       <c r="D84">
-        <v>2280.771012028545</v>
+        <v>2257.221228027996</v>
       </c>
       <c r="E84">
-        <v>4173.414000000001</v>
+        <v>4292.341</v>
       </c>
       <c r="F84">
-        <v>9752.014000000001</v>
+        <v>9870.941000000001</v>
       </c>
       <c r="G84">
         <v>354.7</v>
@@ -8181,37 +8181,37 @@
         <v>706.7</v>
       </c>
       <c r="M84">
-        <v>1958.2044112</v>
+        <v>1982.0849528</v>
       </c>
       <c r="N84">
-        <v>-1251.5044112</v>
+        <v>-1275.3849528</v>
       </c>
       <c r="O84">
-        <v>-125.15044112</v>
+        <v>-127.53849528</v>
       </c>
       <c r="P84">
-        <v>-1126.35397008</v>
+        <v>-1147.84645752</v>
       </c>
       <c r="Q84">
-        <v>-885.5539700800002</v>
+        <v>-907.0464575200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1980673215344264</v>
+        <v>0.2070242228011574</v>
       </c>
       <c r="T84">
-        <v>3.051994418479982</v>
+        <v>3.231523501919982</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.03608918435470839</v>
+        <v>0.03565437490465167</v>
       </c>
       <c r="W84">
-        <v>0.1935532917815745</v>
+        <v>0.193640601519146</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3608918435470839</v>
+        <v>0.3565437490465166</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1959158171370879</v>
+        <v>0.1974658171370879</v>
       </c>
       <c r="C85">
-        <v>-7259.019771972005</v>
+        <v>-7401.015206042954</v>
       </c>
       <c r="D85">
-        <v>2257.221228027996</v>
+        <v>2234.152793957048</v>
       </c>
       <c r="E85">
-        <v>4292.341</v>
+        <v>4411.268000000002</v>
       </c>
       <c r="F85">
-        <v>9870.941000000001</v>
+        <v>9989.868000000002</v>
       </c>
       <c r="G85">
         <v>354.7</v>
@@ -8263,37 +8263,37 @@
         <v>706.7</v>
       </c>
       <c r="M85">
-        <v>1982.0849528</v>
+        <v>2005.965494400001</v>
       </c>
       <c r="N85">
-        <v>-1275.3849528</v>
+        <v>-1299.265494400001</v>
       </c>
       <c r="O85">
-        <v>-127.53849528</v>
+        <v>-129.9265494400001</v>
       </c>
       <c r="P85">
-        <v>-1147.84645752</v>
+        <v>-1169.33894496</v>
       </c>
       <c r="Q85">
-        <v>-907.0464575200001</v>
+        <v>-928.5389449600004</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2070242228011574</v>
+        <v>0.2171007367262297</v>
       </c>
       <c r="T85">
-        <v>3.231523501919982</v>
+        <v>3.433493720789981</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.03565437490465167</v>
+        <v>0.03522991806054866</v>
       </c>
       <c r="W85">
-        <v>0.193640601519146</v>
+        <v>0.1937258324534418</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3565437490465166</v>
+        <v>0.3522991806054866</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1974658171370879</v>
+        <v>0.1990158171370879</v>
       </c>
       <c r="C86">
-        <v>-7401.015206042952</v>
+        <v>-7542.543898840342</v>
       </c>
       <c r="D86">
-        <v>2234.152793957048</v>
+        <v>2211.551101159659</v>
       </c>
       <c r="E86">
-        <v>4411.268</v>
+        <v>4530.195</v>
       </c>
       <c r="F86">
-        <v>9989.868</v>
+        <v>10108.795</v>
       </c>
       <c r="G86">
         <v>354.7</v>
@@ -8345,37 +8345,37 @@
         <v>706.7</v>
       </c>
       <c r="M86">
-        <v>2005.9654944</v>
+        <v>2029.846036</v>
       </c>
       <c r="N86">
-        <v>-1299.2654944</v>
+        <v>-1323.146036</v>
       </c>
       <c r="O86">
-        <v>-129.92654944</v>
+        <v>-132.3146036</v>
       </c>
       <c r="P86">
-        <v>-1169.33894496</v>
+        <v>-1190.8314324</v>
       </c>
       <c r="Q86">
-        <v>-928.5389449600002</v>
+        <v>-950.0314324000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2171007367262296</v>
+        <v>0.2285207858413116</v>
       </c>
       <c r="T86">
-        <v>3.433493720789979</v>
+        <v>3.662393302175977</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.03522991806054867</v>
+        <v>0.03481544843630692</v>
       </c>
       <c r="W86">
-        <v>0.1937258324534418</v>
+        <v>0.1938090579539896</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3522991806054867</v>
+        <v>0.3481544843630692</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1990158171370879</v>
+        <v>0.2005658171370879</v>
       </c>
       <c r="C87">
-        <v>-7542.543898840342</v>
+        <v>-7683.61987378977</v>
       </c>
       <c r="D87">
-        <v>2211.551101159659</v>
+        <v>2189.40212621023</v>
       </c>
       <c r="E87">
-        <v>4530.195</v>
+        <v>4649.121999999999</v>
       </c>
       <c r="F87">
-        <v>10108.795</v>
+        <v>10227.722</v>
       </c>
       <c r="G87">
         <v>354.7</v>
@@ -8427,37 +8427,37 @@
         <v>706.7</v>
       </c>
       <c r="M87">
-        <v>2029.846036</v>
+        <v>2053.7265776</v>
       </c>
       <c r="N87">
-        <v>-1323.146036</v>
+        <v>-1347.0265776</v>
       </c>
       <c r="O87">
-        <v>-132.3146036</v>
+        <v>-134.70265776</v>
       </c>
       <c r="P87">
-        <v>-1190.8314324</v>
+        <v>-1212.32391984</v>
       </c>
       <c r="Q87">
-        <v>-950.0314324000001</v>
+        <v>-971.52391984</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2285207858413116</v>
+        <v>0.2415722705442624</v>
       </c>
       <c r="T87">
-        <v>3.662393302175977</v>
+        <v>3.923992823759976</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.03481544843630692</v>
+        <v>0.03441061764053591</v>
       </c>
       <c r="W87">
-        <v>0.1938090579539896</v>
+        <v>0.1938903479777804</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3481544843630692</v>
+        <v>0.3441061764053591</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2005658171370879</v>
+        <v>0.2021158171370879</v>
       </c>
       <c r="C88">
-        <v>-7683.61987378977</v>
+        <v>-7824.25659810161</v>
       </c>
       <c r="D88">
-        <v>2189.40212621023</v>
+        <v>2167.692401898392</v>
       </c>
       <c r="E88">
-        <v>4649.121999999999</v>
+        <v>4768.049000000001</v>
       </c>
       <c r="F88">
-        <v>10227.722</v>
+        <v>10346.649</v>
       </c>
       <c r="G88">
         <v>354.7</v>
@@ -8509,37 +8509,37 @@
         <v>706.7</v>
       </c>
       <c r="M88">
-        <v>2053.7265776</v>
+        <v>2077.6071192</v>
       </c>
       <c r="N88">
-        <v>-1347.0265776</v>
+        <v>-1370.9071192</v>
       </c>
       <c r="O88">
-        <v>-134.70265776</v>
+        <v>-137.09071192</v>
       </c>
       <c r="P88">
-        <v>-1212.32391984</v>
+        <v>-1233.81640728</v>
       </c>
       <c r="Q88">
-        <v>-971.52391984</v>
+        <v>-993.0164072800003</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2415722705442624</v>
+        <v>0.2566316759707441</v>
       </c>
       <c r="T88">
-        <v>3.923992823759976</v>
+        <v>4.225838425587666</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.03441061764053591</v>
+        <v>0.03401509329984009</v>
       </c>
       <c r="W88">
-        <v>0.1938903479777804</v>
+        <v>0.1939697692653921</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3441061764053591</v>
+        <v>0.3401509329984009</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2021158171370879</v>
+        <v>0.2036658171370879</v>
       </c>
       <c r="C89">
-        <v>-7824.25659810161</v>
+        <v>-7964.467010076887</v>
       </c>
       <c r="D89">
-        <v>2167.692401898392</v>
+        <v>2146.408989923114</v>
       </c>
       <c r="E89">
-        <v>4768.049000000001</v>
+        <v>4886.976000000001</v>
       </c>
       <c r="F89">
-        <v>10346.649</v>
+        <v>10465.576</v>
       </c>
       <c r="G89">
         <v>354.7</v>
@@ -8591,37 +8591,37 @@
         <v>706.7</v>
       </c>
       <c r="M89">
-        <v>2077.6071192</v>
+        <v>2101.4876608</v>
       </c>
       <c r="N89">
-        <v>-1370.9071192</v>
+        <v>-1394.7876608</v>
       </c>
       <c r="O89">
-        <v>-137.09071192</v>
+        <v>-139.47876608</v>
       </c>
       <c r="P89">
-        <v>-1233.81640728</v>
+        <v>-1255.30889472</v>
       </c>
       <c r="Q89">
-        <v>-993.0164072800003</v>
+        <v>-1014.50889472</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2566316759707441</v>
+        <v>0.2742009823016395</v>
       </c>
       <c r="T89">
-        <v>4.225838425587666</v>
+        <v>4.577991627719973</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.03401509329984009</v>
+        <v>0.03362855814870554</v>
       </c>
       <c r="W89">
-        <v>0.1939697692653921</v>
+        <v>0.1940473855237399</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3401509329984009</v>
+        <v>0.3362855814870555</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2036658171370879</v>
+        <v>0.2052158171370879</v>
       </c>
       <c r="C90">
-        <v>-7964.467010076887</v>
+        <v>-8104.263544820232</v>
       </c>
       <c r="D90">
-        <v>2146.408989923114</v>
+        <v>2125.539455179769</v>
       </c>
       <c r="E90">
-        <v>4886.976000000001</v>
+        <v>5005.903</v>
       </c>
       <c r="F90">
-        <v>10465.576</v>
+        <v>10584.503</v>
       </c>
       <c r="G90">
         <v>354.7</v>
@@ -8673,37 +8673,37 @@
         <v>706.7</v>
       </c>
       <c r="M90">
-        <v>2101.4876608</v>
+        <v>2125.3682024</v>
       </c>
       <c r="N90">
-        <v>-1394.7876608</v>
+        <v>-1418.6682024</v>
       </c>
       <c r="O90">
-        <v>-139.47876608</v>
+        <v>-141.86682024</v>
       </c>
       <c r="P90">
-        <v>-1255.30889472</v>
+        <v>-1276.80138216</v>
       </c>
       <c r="Q90">
-        <v>-1014.50889472</v>
+        <v>-1036.00138216</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2742009823016395</v>
+        <v>0.294964707965425</v>
       </c>
       <c r="T90">
-        <v>4.577991627719973</v>
+        <v>4.994172684785426</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.03362855814870554</v>
+        <v>0.03325070918074257</v>
       </c>
       <c r="W90">
-        <v>0.1940473855237399</v>
+        <v>0.1941232575965069</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3362855814870555</v>
+        <v>0.3325070918074257</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2052158171370879</v>
+        <v>0.2067658171370879</v>
       </c>
       <c r="C91">
-        <v>-8104.263544820232</v>
+        <v>-8243.658158467186</v>
       </c>
       <c r="D91">
-        <v>2125.539455179769</v>
+        <v>2105.071841532814</v>
       </c>
       <c r="E91">
-        <v>5005.903</v>
+        <v>5124.83</v>
       </c>
       <c r="F91">
-        <v>10584.503</v>
+        <v>10703.43</v>
       </c>
       <c r="G91">
         <v>354.7</v>
@@ -8755,37 +8755,37 @@
         <v>706.7</v>
       </c>
       <c r="M91">
-        <v>2125.3682024</v>
+        <v>2149.248744</v>
       </c>
       <c r="N91">
-        <v>-1418.6682024</v>
+        <v>-1442.548744</v>
       </c>
       <c r="O91">
-        <v>-141.86682024</v>
+        <v>-144.2548744</v>
       </c>
       <c r="P91">
-        <v>-1276.80138216</v>
+        <v>-1298.2938696</v>
       </c>
       <c r="Q91">
-        <v>-1036.00138216</v>
+        <v>-1057.4938696</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.294964707965425</v>
+        <v>0.3198811787619675</v>
       </c>
       <c r="T91">
-        <v>4.994172684785426</v>
+        <v>5.493589953263968</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.03325070918074257</v>
+        <v>0.03288125685651209</v>
       </c>
       <c r="W91">
-        <v>0.1941232575965069</v>
+        <v>0.1941974436232124</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3325070918074257</v>
+        <v>0.328812568565121</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2067658171370879</v>
+        <v>0.2083158171370879</v>
       </c>
       <c r="C92">
-        <v>-8243.658158467186</v>
+        <v>-8382.662351025148</v>
       </c>
       <c r="D92">
-        <v>2105.071841532814</v>
+        <v>2084.994648974853</v>
       </c>
       <c r="E92">
-        <v>5124.83</v>
+        <v>5243.757000000001</v>
       </c>
       <c r="F92">
-        <v>10703.43</v>
+        <v>10822.357</v>
       </c>
       <c r="G92">
         <v>354.7</v>
@@ -8837,37 +8837,37 @@
         <v>706.7</v>
       </c>
       <c r="M92">
-        <v>2149.248744</v>
+        <v>2173.1292856</v>
       </c>
       <c r="N92">
-        <v>-1442.548744</v>
+        <v>-1466.4292856</v>
       </c>
       <c r="O92">
-        <v>-144.2548744</v>
+        <v>-146.6429285600001</v>
       </c>
       <c r="P92">
-        <v>-1298.2938696</v>
+        <v>-1319.78635704</v>
       </c>
       <c r="Q92">
-        <v>-1057.4938696</v>
+        <v>-1078.98635704</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3198811787619675</v>
+        <v>0.3503346430688528</v>
       </c>
       <c r="T92">
-        <v>5.493589953263968</v>
+        <v>6.103988836959965</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.03288125685651209</v>
+        <v>0.03251992436358338</v>
       </c>
       <c r="W92">
-        <v>0.1941974436232124</v>
+        <v>0.1942699991877924</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.328812568565121</v>
+        <v>0.3251992436358339</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2083158171370879</v>
+        <v>0.2098658171370879</v>
       </c>
       <c r="C93">
-        <v>-8382.662351025148</v>
+        <v>-8521.287187919541</v>
       </c>
       <c r="D93">
-        <v>2084.994648974853</v>
+        <v>2065.296812080462</v>
       </c>
       <c r="E93">
-        <v>5243.757000000001</v>
+        <v>5362.684000000001</v>
       </c>
       <c r="F93">
-        <v>10822.357</v>
+        <v>10941.284</v>
       </c>
       <c r="G93">
         <v>354.7</v>
@@ -8919,37 +8919,37 @@
         <v>706.7</v>
       </c>
       <c r="M93">
-        <v>2173.1292856</v>
+        <v>2197.0098272</v>
       </c>
       <c r="N93">
-        <v>-1466.4292856</v>
+        <v>-1490.3098272</v>
       </c>
       <c r="O93">
-        <v>-146.6429285600001</v>
+        <v>-149.0309827200001</v>
       </c>
       <c r="P93">
-        <v>-1319.78635704</v>
+        <v>-1341.27884448</v>
       </c>
       <c r="Q93">
-        <v>-1078.98635704</v>
+        <v>-1100.47884448</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3503346430688528</v>
+        <v>0.3884014734524594</v>
       </c>
       <c r="T93">
-        <v>6.103988836959965</v>
+        <v>6.866987441579962</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.03251992436358338</v>
+        <v>0.03216644692484878</v>
       </c>
       <c r="W93">
-        <v>0.1942699991877924</v>
+        <v>0.1943409774574903</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3251992436358339</v>
+        <v>0.3216644692484878</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2098658171370879</v>
+        <v>0.2114158171370879</v>
       </c>
       <c r="C94">
-        <v>-8521.287187919541</v>
+        <v>-8659.543320330093</v>
       </c>
       <c r="D94">
-        <v>2065.296812080462</v>
+        <v>2045.967679669909</v>
       </c>
       <c r="E94">
-        <v>5362.684000000001</v>
+        <v>5481.611000000001</v>
       </c>
       <c r="F94">
-        <v>10941.284</v>
+        <v>11060.211</v>
       </c>
       <c r="G94">
         <v>354.7</v>
@@ -9001,37 +9001,37 @@
         <v>706.7</v>
       </c>
       <c r="M94">
-        <v>2197.0098272</v>
+        <v>2220.8903688</v>
       </c>
       <c r="N94">
-        <v>-1490.3098272</v>
+        <v>-1514.1903688</v>
       </c>
       <c r="O94">
-        <v>-149.0309827200001</v>
+        <v>-151.41903688</v>
       </c>
       <c r="P94">
-        <v>-1341.27884448</v>
+        <v>-1362.77133192</v>
       </c>
       <c r="Q94">
-        <v>-1100.47884448</v>
+        <v>-1121.97133192</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3884014734524594</v>
+        <v>0.4373445410885251</v>
       </c>
       <c r="T94">
-        <v>6.866987441579962</v>
+        <v>7.847985647519958</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.03216644692484878</v>
+        <v>0.03182057115146331</v>
       </c>
       <c r="W94">
-        <v>0.1943409774574903</v>
+        <v>0.1944104293127862</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3216644692484878</v>
+        <v>0.3182057115146331</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2114158171370879</v>
+        <v>0.2129658171370879</v>
       </c>
       <c r="C95">
-        <v>-8659.543320330093</v>
+        <v>-8797.441004395769</v>
       </c>
       <c r="D95">
-        <v>2045.967679669909</v>
+        <v>2026.996995604232</v>
       </c>
       <c r="E95">
-        <v>5481.611000000001</v>
+        <v>5600.538</v>
       </c>
       <c r="F95">
-        <v>11060.211</v>
+        <v>11179.138</v>
       </c>
       <c r="G95">
         <v>354.7</v>
@@ -9083,37 +9083,37 @@
         <v>706.7</v>
       </c>
       <c r="M95">
-        <v>2220.8903688</v>
+        <v>2244.7709104</v>
       </c>
       <c r="N95">
-        <v>-1514.1903688</v>
+        <v>-1538.0709104</v>
       </c>
       <c r="O95">
-        <v>-151.41903688</v>
+        <v>-153.80709104</v>
       </c>
       <c r="P95">
-        <v>-1362.77133192</v>
+        <v>-1384.26381936</v>
       </c>
       <c r="Q95">
-        <v>-1121.97133192</v>
+        <v>-1143.46381936</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4373445410885251</v>
+        <v>0.5026019646032793</v>
       </c>
       <c r="T95">
-        <v>7.847985647519958</v>
+        <v>9.155983255439953</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.03182057115146331</v>
+        <v>0.03148205443708604</v>
       </c>
       <c r="W95">
-        <v>0.1944104293127862</v>
+        <v>0.1944784034690331</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3182057115146331</v>
+        <v>0.3148205443708605</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2129658171370879</v>
+        <v>0.2145158171370879</v>
       </c>
       <c r="C96">
-        <v>-8797.441004395769</v>
+        <v>-8934.990119361042</v>
       </c>
       <c r="D96">
-        <v>2026.996995604232</v>
+        <v>2008.374880638959</v>
       </c>
       <c r="E96">
-        <v>5600.538</v>
+        <v>5719.465000000002</v>
       </c>
       <c r="F96">
-        <v>11179.138</v>
+        <v>11298.065</v>
       </c>
       <c r="G96">
         <v>354.7</v>
@@ -9165,37 +9165,37 @@
         <v>706.7</v>
       </c>
       <c r="M96">
-        <v>2244.7709104</v>
+        <v>2268.651452000001</v>
       </c>
       <c r="N96">
-        <v>-1538.0709104</v>
+        <v>-1561.951452</v>
       </c>
       <c r="O96">
-        <v>-153.80709104</v>
+        <v>-156.1951452000001</v>
       </c>
       <c r="P96">
-        <v>-1384.26381936</v>
+        <v>-1405.7563068</v>
       </c>
       <c r="Q96">
-        <v>-1143.46381936</v>
+        <v>-1164.9563068</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5026019646032793</v>
+        <v>0.5939623575239356</v>
       </c>
       <c r="T96">
-        <v>9.155983255439953</v>
+        <v>10.98717990652795</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.03148205443708604</v>
+        <v>0.03115066439037988</v>
       </c>
       <c r="W96">
-        <v>0.1944784034690331</v>
+        <v>0.1945449465904117</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3148205443708605</v>
+        <v>0.3115066439037987</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2145158171370879</v>
+        <v>0.2160658171370879</v>
       </c>
       <c r="C97">
-        <v>-8934.990119361042</v>
+        <v>-9072.20018473102</v>
       </c>
       <c r="D97">
-        <v>2008.374880638959</v>
+        <v>1990.091815268982</v>
       </c>
       <c r="E97">
-        <v>5719.465000000002</v>
+        <v>5838.392000000002</v>
       </c>
       <c r="F97">
-        <v>11298.065</v>
+        <v>11416.992</v>
       </c>
       <c r="G97">
         <v>354.7</v>
@@ -9247,37 +9247,37 @@
         <v>706.7</v>
       </c>
       <c r="M97">
-        <v>2268.651452000001</v>
+        <v>2292.531993600001</v>
       </c>
       <c r="N97">
-        <v>-1561.951452</v>
+        <v>-1585.8319936</v>
       </c>
       <c r="O97">
-        <v>-156.1951452000001</v>
+        <v>-158.5831993600001</v>
       </c>
       <c r="P97">
-        <v>-1405.7563068</v>
+        <v>-1427.248794240001</v>
       </c>
       <c r="Q97">
-        <v>-1164.9563068</v>
+        <v>-1186.448794240001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5939623575239356</v>
+        <v>0.7310029469049196</v>
       </c>
       <c r="T97">
-        <v>10.98717990652795</v>
+        <v>13.73397488315994</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.03115066439037988</v>
+        <v>0.03082617830298008</v>
       </c>
       <c r="W97">
-        <v>0.1945449465904117</v>
+        <v>0.1946101033967616</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3115066439037987</v>
+        <v>0.3082617830298008</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2160658171370879</v>
+        <v>0.2176158171370879</v>
       </c>
       <c r="C98">
-        <v>-9072.20018473102</v>
+        <v>-9209.080376498023</v>
       </c>
       <c r="D98">
-        <v>1990.091815268981</v>
+        <v>1972.138623501977</v>
       </c>
       <c r="E98">
-        <v>5838.392</v>
+        <v>5957.319</v>
       </c>
       <c r="F98">
-        <v>11416.992</v>
+        <v>11535.919</v>
       </c>
       <c r="G98">
         <v>354.7</v>
@@ -9329,37 +9329,37 @@
         <v>706.7</v>
       </c>
       <c r="M98">
-        <v>2292.5319936</v>
+        <v>2316.4125352</v>
       </c>
       <c r="N98">
-        <v>-1585.8319936</v>
+        <v>-1609.7125352</v>
       </c>
       <c r="O98">
-        <v>-158.58319936</v>
+        <v>-160.97125352</v>
       </c>
       <c r="P98">
-        <v>-1427.24879424</v>
+        <v>-1448.74128168</v>
       </c>
       <c r="Q98">
-        <v>-1186.44879424</v>
+        <v>-1207.94128168</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7310029469049178</v>
+        <v>0.9594039292065574</v>
       </c>
       <c r="T98">
-        <v>13.73397488315991</v>
+        <v>18.31196651087988</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.03082617830298008</v>
+        <v>0.03050838265037205</v>
       </c>
       <c r="W98">
-        <v>0.1946101033967616</v>
+        <v>0.1946739167638053</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3082617830298009</v>
+        <v>0.3050838265037205</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2176158171370879</v>
+        <v>0.2191658171370879</v>
       </c>
       <c r="C99">
-        <v>-9209.080376498023</v>
+        <v>-9345.639542497687</v>
       </c>
       <c r="D99">
-        <v>1972.138623501977</v>
+        <v>1954.506457502315</v>
       </c>
       <c r="E99">
-        <v>5957.319</v>
+        <v>6076.246000000001</v>
       </c>
       <c r="F99">
-        <v>11535.919</v>
+        <v>11654.846</v>
       </c>
       <c r="G99">
         <v>354.7</v>
@@ -9411,37 +9411,37 @@
         <v>706.7</v>
       </c>
       <c r="M99">
-        <v>2316.4125352</v>
+        <v>2340.293076800001</v>
       </c>
       <c r="N99">
-        <v>-1609.7125352</v>
+        <v>-1633.593076800001</v>
       </c>
       <c r="O99">
-        <v>-160.97125352</v>
+        <v>-163.3593076800001</v>
       </c>
       <c r="P99">
-        <v>-1448.74128168</v>
+        <v>-1470.23376912</v>
       </c>
       <c r="Q99">
-        <v>-1207.94128168</v>
+        <v>-1229.433769120001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9594039292065574</v>
+        <v>1.416205893809836</v>
       </c>
       <c r="T99">
-        <v>18.31196651087988</v>
+        <v>27.46794976631981</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.03050838265037205</v>
+        <v>0.03019707262332743</v>
       </c>
       <c r="W99">
-        <v>0.1946739167638053</v>
+        <v>0.1947364278172359</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3050838265037205</v>
+        <v>0.3019707262332743</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2191658171370879</v>
+        <v>0.2207158171370879</v>
       </c>
       <c r="C100">
-        <v>-9345.639542497687</v>
+        <v>-9481.886216948595</v>
       </c>
       <c r="D100">
-        <v>1954.506457502315</v>
+        <v>1937.186783051407</v>
       </c>
       <c r="E100">
-        <v>6076.246000000001</v>
+        <v>6195.173000000001</v>
       </c>
       <c r="F100">
-        <v>11654.846</v>
+        <v>11773.773</v>
       </c>
       <c r="G100">
         <v>354.7</v>
@@ -9493,37 +9493,37 @@
         <v>706.7</v>
       </c>
       <c r="M100">
-        <v>2340.293076800001</v>
+        <v>2364.1736184</v>
       </c>
       <c r="N100">
-        <v>-1633.593076800001</v>
+        <v>-1657.4736184</v>
       </c>
       <c r="O100">
-        <v>-163.3593076800001</v>
+        <v>-165.74736184</v>
       </c>
       <c r="P100">
-        <v>-1470.23376912</v>
+        <v>-1491.72625656</v>
       </c>
       <c r="Q100">
-        <v>-1229.433769120001</v>
+        <v>-1250.92625656</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.416205893809836</v>
+        <v>2.786611787619671</v>
       </c>
       <c r="T100">
-        <v>27.46794976631981</v>
+        <v>54.93589953263962</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.03019707262332743</v>
+        <v>0.02989205168773826</v>
       </c>
       <c r="W100">
-        <v>0.1947364278172359</v>
+        <v>0.1947976760211022</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3019707262332743</v>
+        <v>0.2989205168773826</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2207158171370879</v>
-      </c>
-      <c r="C101">
-        <v>-9481.886216948595</v>
-      </c>
-      <c r="D101">
-        <v>1937.186783051407</v>
-      </c>
-      <c r="E101">
-        <v>6195.173000000001</v>
-      </c>
-      <c r="F101">
-        <v>11773.773</v>
-      </c>
-      <c r="G101">
-        <v>354.7</v>
-      </c>
-      <c r="H101">
-        <v>6314.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>947.5</v>
-      </c>
-      <c r="K101">
-        <v>240.8</v>
-      </c>
-      <c r="L101">
-        <v>706.7</v>
-      </c>
-      <c r="M101">
-        <v>2364.1736184</v>
-      </c>
-      <c r="N101">
-        <v>-1657.4736184</v>
-      </c>
-      <c r="O101">
-        <v>-165.74736184</v>
-      </c>
-      <c r="P101">
-        <v>-1491.72625656</v>
-      </c>
-      <c r="Q101">
-        <v>-1250.92625656</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.786611787619671</v>
-      </c>
-      <c r="T101">
-        <v>54.93589953263962</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.02989205168773826</v>
-      </c>
-      <c r="W101">
-        <v>0.1947976760211022</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2989205168773826</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
